--- a/research/traditional_assets/database/data/germany/germany_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_beverage_soft.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07421564215721096</v>
+        <v>0.07402449523073934</v>
       </c>
       <c r="C2">
-        <v>108.5716246765229</v>
+        <v>107.9175863897555</v>
       </c>
       <c r="D2">
-        <v>105.6516246765229</v>
+        <v>106.1425850885735</v>
       </c>
       <c r="E2">
-        <v>-16.09986988179993</v>
+        <v>-14.95487118298193</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.144998698817999</v>
       </c>
       <c r="G2">
         <v>2.92</v>
@@ -1451,28 +1451,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05759343455054537</v>
       </c>
       <c r="N2">
-        <v>7.609999999999999</v>
+        <v>7.552406565449454</v>
       </c>
       <c r="O2">
-        <v>2.283</v>
+        <v>2.265721969634836</v>
       </c>
       <c r="P2">
-        <v>5.327</v>
+        <v>5.286684595814618</v>
       </c>
       <c r="Q2">
-        <v>18.127</v>
+        <v>18.08668459581462</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07421564215721096</v>
+        <v>0.07441656083913065</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6608905505572897</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>132.1331165503124</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07402449523073934</v>
+        <v>0.0738333483042677</v>
       </c>
       <c r="C3">
-        <v>107.9175863897555</v>
+        <v>107.2681323670357</v>
       </c>
       <c r="D3">
-        <v>106.1425850885735</v>
+        <v>106.6381297646717</v>
       </c>
       <c r="E3">
-        <v>-14.95487118298193</v>
+        <v>-13.80987248416393</v>
       </c>
       <c r="F3">
-        <v>1.144998698817999</v>
+        <v>2.289997397635999</v>
       </c>
       <c r="G3">
         <v>2.92</v>
@@ -1533,28 +1533,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M3">
-        <v>0.05759343455054537</v>
+        <v>0.1151868691010907</v>
       </c>
       <c r="N3">
-        <v>7.552406565449454</v>
+        <v>7.494813130898908</v>
       </c>
       <c r="O3">
-        <v>2.265721969634836</v>
+        <v>2.248443939269672</v>
       </c>
       <c r="P3">
-        <v>5.286684595814618</v>
+        <v>5.246369191629237</v>
       </c>
       <c r="Q3">
-        <v>18.08668459581462</v>
+        <v>18.04636919162924</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07441656083913065</v>
+        <v>0.07462157990231398</v>
       </c>
       <c r="T3">
-        <v>0.6608905505572897</v>
+        <v>0.6656254019010159</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>132.1331165503124</v>
+        <v>66.0665582751562</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0738333483042677</v>
+        <v>0.07364220137779606</v>
       </c>
       <c r="C4">
-        <v>107.2681323670357</v>
+        <v>106.6233271167766</v>
       </c>
       <c r="D4">
-        <v>106.6381297646717</v>
+        <v>107.1383232132305</v>
       </c>
       <c r="E4">
-        <v>-13.80987248416393</v>
+        <v>-12.66487378534593</v>
       </c>
       <c r="F4">
-        <v>2.289997397635999</v>
+        <v>3.434996096453998</v>
       </c>
       <c r="G4">
         <v>2.92</v>
@@ -1615,28 +1615,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M4">
-        <v>0.1151868691010907</v>
+        <v>0.1727803036516361</v>
       </c>
       <c r="N4">
-        <v>7.494813130898908</v>
+        <v>7.437219696348364</v>
       </c>
       <c r="O4">
-        <v>2.248443939269672</v>
+        <v>2.231165908904509</v>
       </c>
       <c r="P4">
-        <v>5.246369191629237</v>
+        <v>5.206053787443855</v>
       </c>
       <c r="Q4">
-        <v>18.04636919162924</v>
+        <v>18.00605378744385</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07462157990231398</v>
+        <v>0.07483082616267636</v>
       </c>
       <c r="T4">
-        <v>0.6656254019010159</v>
+        <v>0.6704578790456436</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>66.0665582751562</v>
+        <v>44.04437218343747</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07364220137779606</v>
+        <v>0.07345105445132444</v>
       </c>
       <c r="C5">
-        <v>106.6233271167766</v>
+        <v>105.9832363634195</v>
       </c>
       <c r="D5">
-        <v>107.1383232132305</v>
+        <v>107.6432311586915</v>
       </c>
       <c r="E5">
-        <v>-12.66487378534593</v>
+        <v>-11.51987508652794</v>
       </c>
       <c r="F5">
-        <v>3.434996096453998</v>
+        <v>4.579994795271998</v>
       </c>
       <c r="G5">
         <v>2.92</v>
@@ -1697,28 +1697,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M5">
-        <v>0.1727803036516361</v>
+        <v>0.2303737382021815</v>
       </c>
       <c r="N5">
-        <v>7.437219696348364</v>
+        <v>7.379626261797818</v>
       </c>
       <c r="O5">
-        <v>2.231165908904509</v>
+        <v>2.213887878539345</v>
       </c>
       <c r="P5">
-        <v>5.206053787443855</v>
+        <v>5.165738383258473</v>
       </c>
       <c r="Q5">
-        <v>18.00605378744385</v>
+        <v>17.96573838325848</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07483082616267636</v>
+        <v>0.07504443172012962</v>
       </c>
       <c r="T5">
-        <v>0.6704578790456436</v>
+        <v>0.6753910327974509</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.04437218343747</v>
+        <v>33.0332791375781</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07345105445132444</v>
+        <v>0.0732599075248528</v>
       </c>
       <c r="C6">
-        <v>105.9832363634195</v>
+        <v>105.3479270762239</v>
       </c>
       <c r="D6">
-        <v>107.6432311586915</v>
+        <v>108.1529205703139</v>
       </c>
       <c r="E6">
-        <v>-11.51987508652794</v>
+        <v>-10.37487638770994</v>
       </c>
       <c r="F6">
-        <v>4.579994795271998</v>
+        <v>5.724993494089997</v>
       </c>
       <c r="G6">
         <v>2.92</v>
@@ -1779,28 +1779,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M6">
-        <v>0.2303737382021815</v>
+        <v>0.2879671727527268</v>
       </c>
       <c r="N6">
-        <v>7.379626261797818</v>
+        <v>7.322032827247273</v>
       </c>
       <c r="O6">
-        <v>2.213887878539345</v>
+        <v>2.196609848174182</v>
       </c>
       <c r="P6">
-        <v>5.165738383258473</v>
+        <v>5.125422979073091</v>
       </c>
       <c r="Q6">
-        <v>17.96573838325848</v>
+        <v>17.92542297907309</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07504443172012962</v>
+        <v>0.07526253423668716</v>
       </c>
       <c r="T6">
-        <v>0.6753910327974509</v>
+        <v>0.6804280424177175</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.0332791375781</v>
+        <v>26.42662331006248</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0732599075248528</v>
+        <v>0.07306876059838117</v>
       </c>
       <c r="C7">
-        <v>105.3479270762239</v>
+        <v>104.7174674988779</v>
       </c>
       <c r="D7">
-        <v>108.1529205703139</v>
+        <v>108.6674596917859</v>
       </c>
       <c r="E7">
-        <v>-10.37487638770994</v>
+        <v>-9.229877688891936</v>
       </c>
       <c r="F7">
-        <v>5.724993494089997</v>
+        <v>6.869992192907997</v>
       </c>
       <c r="G7">
         <v>2.92</v>
@@ -1861,28 +1861,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M7">
-        <v>0.2879671727527268</v>
+        <v>0.3455606073032722</v>
       </c>
       <c r="N7">
-        <v>7.322032827247273</v>
+        <v>7.264439392696727</v>
       </c>
       <c r="O7">
-        <v>2.196609848174182</v>
+        <v>2.179331817809018</v>
       </c>
       <c r="P7">
-        <v>5.125422979073091</v>
+        <v>5.085107574887709</v>
       </c>
       <c r="Q7">
-        <v>17.92542297907309</v>
+        <v>17.88510757488771</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07526253423668716</v>
+        <v>0.0754852772323204</v>
       </c>
       <c r="T7">
-        <v>0.6804280424177175</v>
+        <v>0.6855722224554365</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.42662331006248</v>
+        <v>22.02218609171873</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07306876059838117</v>
+        <v>0.07287761367190954</v>
       </c>
       <c r="C8">
-        <v>104.7174674988779</v>
+        <v>104.0919271799593</v>
       </c>
       <c r="D8">
-        <v>108.6674596917859</v>
+        <v>109.1869180716853</v>
       </c>
       <c r="E8">
-        <v>-9.229877688891936</v>
+        <v>-8.084878990073937</v>
       </c>
       <c r="F8">
-        <v>6.869992192907996</v>
+        <v>8.014990891725995</v>
       </c>
       <c r="G8">
         <v>2.92</v>
@@ -1943,28 +1943,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M8">
-        <v>0.3455606073032722</v>
+        <v>0.4031540418538175</v>
       </c>
       <c r="N8">
-        <v>7.264439392696727</v>
+        <v>7.206845958146182</v>
       </c>
       <c r="O8">
-        <v>2.179331817809018</v>
+        <v>2.162053787443855</v>
       </c>
       <c r="P8">
-        <v>5.085107574887709</v>
+        <v>5.044792170702328</v>
       </c>
       <c r="Q8">
-        <v>17.88510757488771</v>
+        <v>17.84479217070233</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0754852772323204</v>
+        <v>0.07571281039990273</v>
       </c>
       <c r="T8">
-        <v>0.6855722224554365</v>
+        <v>0.6908270300208484</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.02218609171873</v>
+        <v>18.87615950718749</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07287761367190954</v>
+        <v>0.07268646674543791</v>
       </c>
       <c r="C9">
-        <v>104.0919271799593</v>
+        <v>103.4713770042736</v>
       </c>
       <c r="D9">
-        <v>109.1869180716853</v>
+        <v>109.7113665948176</v>
       </c>
       <c r="E9">
-        <v>-8.084878990073936</v>
+        <v>-6.939880291255937</v>
       </c>
       <c r="F9">
-        <v>8.014990891725997</v>
+        <v>9.159989590543995</v>
       </c>
       <c r="G9">
         <v>2.92</v>
@@ -2025,28 +2025,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M9">
-        <v>0.4031540418538176</v>
+        <v>0.4607474764043629</v>
       </c>
       <c r="N9">
-        <v>7.206845958146181</v>
+        <v>7.149252523595637</v>
       </c>
       <c r="O9">
-        <v>2.162053787443854</v>
+        <v>2.144775757078691</v>
       </c>
       <c r="P9">
-        <v>5.044792170702327</v>
+        <v>5.004476766516946</v>
       </c>
       <c r="Q9">
-        <v>17.84479217070233</v>
+        <v>17.80447676651695</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07571281039990273</v>
+        <v>0.07594528994069338</v>
       </c>
       <c r="T9">
-        <v>0.6908270300208484</v>
+        <v>0.6961960725333345</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.87615950718748</v>
+        <v>16.51663956878905</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07268646674543791</v>
+        <v>0.07249531981896629</v>
       </c>
       <c r="C10">
-        <v>103.4713770042736</v>
+        <v>102.8558892250999</v>
       </c>
       <c r="D10">
-        <v>109.7113665948176</v>
+        <v>110.2408775144619</v>
       </c>
       <c r="E10">
-        <v>-6.939880291255937</v>
+        <v>-5.794881592437939</v>
       </c>
       <c r="F10">
-        <v>9.159989590543995</v>
+        <v>10.30498828936199</v>
       </c>
       <c r="G10">
         <v>2.92</v>
@@ -2107,28 +2107,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M10">
-        <v>0.4607474764043629</v>
+        <v>0.5183409109549083</v>
       </c>
       <c r="N10">
-        <v>7.149252523595637</v>
+        <v>7.091659089045091</v>
       </c>
       <c r="O10">
-        <v>2.144775757078691</v>
+        <v>2.127497726713527</v>
       </c>
       <c r="P10">
-        <v>5.004476766516946</v>
+        <v>4.964161362331565</v>
       </c>
       <c r="Q10">
-        <v>17.80447676651695</v>
+        <v>17.76416136233156</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07594528994069338</v>
+        <v>0.07618287892194096</v>
       </c>
       <c r="T10">
-        <v>0.6961960725333345</v>
+        <v>0.7016831159801609</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.51663956878905</v>
+        <v>14.68145739447916</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07249531981896629</v>
+        <v>0.07230417289249465</v>
       </c>
       <c r="C11">
-        <v>102.8558892250999</v>
+        <v>102.2455374973753</v>
       </c>
       <c r="D11">
-        <v>110.2408775144619</v>
+        <v>110.7755244855553</v>
       </c>
       <c r="E11">
-        <v>-5.794881592437939</v>
+        <v>-4.649882893619941</v>
       </c>
       <c r="F11">
-        <v>10.30498828936199</v>
+        <v>11.44998698817999</v>
       </c>
       <c r="G11">
         <v>2.92</v>
@@ -2189,28 +2189,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M11">
-        <v>0.5183409109549083</v>
+        <v>0.5759343455054535</v>
       </c>
       <c r="N11">
-        <v>7.091659089045091</v>
+        <v>7.034065654494546</v>
       </c>
       <c r="O11">
-        <v>2.127497726713527</v>
+        <v>2.110219696348364</v>
       </c>
       <c r="P11">
-        <v>4.964161362331565</v>
+        <v>4.923845958146182</v>
       </c>
       <c r="Q11">
-        <v>17.76416136233156</v>
+        <v>17.72384595814618</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07618287892194096</v>
+        <v>0.07642574765832738</v>
       </c>
       <c r="T11">
-        <v>0.7016831159801609</v>
+        <v>0.7072920937258056</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.68145739447916</v>
+        <v>13.21331165503124</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07230417289249465</v>
+        <v>0.072228525966023</v>
       </c>
       <c r="C12">
-        <v>102.2455374973753</v>
+        <v>101.31356184211</v>
       </c>
       <c r="D12">
-        <v>110.7755244855553</v>
+        <v>110.988547529108</v>
       </c>
       <c r="E12">
-        <v>-4.649882893619939</v>
+        <v>-3.504884194801939</v>
       </c>
       <c r="F12">
-        <v>11.44998698817999</v>
+        <v>12.59498568699799</v>
       </c>
       <c r="G12">
         <v>2.92</v>
@@ -2271,45 +2271,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M12">
-        <v>0.5759343455054536</v>
+        <v>0.6524202585864961</v>
       </c>
       <c r="N12">
-        <v>7.034065654494546</v>
+        <v>6.957579741413503</v>
       </c>
       <c r="O12">
-        <v>2.110219696348364</v>
+        <v>2.087273922424051</v>
       </c>
       <c r="P12">
-        <v>4.923845958146182</v>
+        <v>4.870305818989452</v>
       </c>
       <c r="Q12">
-        <v>17.72384595814618</v>
+        <v>17.67030581898945</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07642574765832738</v>
+        <v>0.07667407411912697</v>
       </c>
       <c r="T12">
-        <v>0.7072920937258056</v>
+        <v>0.7130271159151728</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.21331165503124</v>
+        <v>11.66426072741438</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.072228525966023</v>
+        <v>0.07204787903955137</v>
       </c>
       <c r="C13">
-        <v>101.31356184211</v>
+        <v>100.6805976081425</v>
       </c>
       <c r="D13">
-        <v>110.988547529108</v>
+        <v>111.5005819939585</v>
       </c>
       <c r="E13">
-        <v>-3.504884194801939</v>
+        <v>-2.35988549598394</v>
       </c>
       <c r="F13">
-        <v>12.59498568699799</v>
+        <v>13.73998438581599</v>
       </c>
       <c r="G13">
         <v>2.92</v>
@@ -2353,28 +2353,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M13">
-        <v>0.6524202585864961</v>
+        <v>0.7117311911852684</v>
       </c>
       <c r="N13">
-        <v>6.957579741413503</v>
+        <v>6.898268808814731</v>
       </c>
       <c r="O13">
-        <v>2.087273922424051</v>
+        <v>2.069480642644419</v>
       </c>
       <c r="P13">
-        <v>4.870305818989452</v>
+        <v>4.828788166170312</v>
       </c>
       <c r="Q13">
-        <v>17.67030581898945</v>
+        <v>17.62878816617031</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07667407411912697</v>
+        <v>0.07692804436312656</v>
       </c>
       <c r="T13">
-        <v>0.7130271159151728</v>
+        <v>0.7188924795179347</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.66426072741438</v>
+        <v>10.69223900012985</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07204787903955137</v>
+        <v>0.07186723211307974</v>
       </c>
       <c r="C14">
-        <v>100.6805976081425</v>
+        <v>100.0523797095891</v>
       </c>
       <c r="D14">
-        <v>111.5005819939585</v>
+        <v>112.0173627942231</v>
       </c>
       <c r="E14">
-        <v>-2.35988549598394</v>
+        <v>-1.21488679716594</v>
       </c>
       <c r="F14">
-        <v>13.73998438581599</v>
+        <v>14.88498308463399</v>
       </c>
       <c r="G14">
         <v>2.92</v>
@@ -2435,28 +2435,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M14">
-        <v>0.7117311911852684</v>
+        <v>0.7710421237840408</v>
       </c>
       <c r="N14">
-        <v>6.898268808814731</v>
+        <v>6.838957876215959</v>
       </c>
       <c r="O14">
-        <v>2.069480642644419</v>
+        <v>2.051687362864788</v>
       </c>
       <c r="P14">
-        <v>4.828788166170312</v>
+        <v>4.787270513351171</v>
       </c>
       <c r="Q14">
-        <v>17.62878816617031</v>
+        <v>17.58727051335117</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07692804436312656</v>
+        <v>0.07718785300353993</v>
       </c>
       <c r="T14">
-        <v>0.7188924795179347</v>
+        <v>0.7248926790655875</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.69223900012985</v>
+        <v>9.869759077042936</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07186723211307974</v>
+        <v>0.0718531851866081</v>
       </c>
       <c r="C15">
-        <v>100.0523797095891</v>
+        <v>98.9477661754604</v>
       </c>
       <c r="D15">
-        <v>112.0173627942231</v>
+        <v>112.0577479589124</v>
       </c>
       <c r="E15">
-        <v>-1.21488679716594</v>
+        <v>-0.06988809834793841</v>
       </c>
       <c r="F15">
-        <v>14.88498308463399</v>
+        <v>16.02998178345199</v>
       </c>
       <c r="G15">
         <v>2.92</v>
@@ -2517,45 +2517,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M15">
-        <v>0.7710421237840408</v>
+        <v>0.8576040254146817</v>
       </c>
       <c r="N15">
-        <v>6.838957876215959</v>
+        <v>6.752395974585317</v>
       </c>
       <c r="O15">
-        <v>2.051687362864788</v>
+        <v>2.025718792375595</v>
       </c>
       <c r="P15">
-        <v>4.787270513351171</v>
+        <v>4.726677182209722</v>
       </c>
       <c r="Q15">
-        <v>17.58727051335117</v>
+        <v>17.52667718220972</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07718785300353993</v>
+        <v>0.07745370370535826</v>
       </c>
       <c r="T15">
-        <v>0.7248926790655875</v>
+        <v>0.7310324181376044</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.869759077042936</v>
+        <v>8.87355909543486</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0718531851866081</v>
+        <v>0.07168443826013647</v>
       </c>
       <c r="C16">
-        <v>98.9477661754604</v>
+        <v>98.29020391713345</v>
       </c>
       <c r="D16">
-        <v>112.0577479589124</v>
+        <v>112.5451843994034</v>
       </c>
       <c r="E16">
-        <v>-0.06988809834793841</v>
+        <v>1.075110600470062</v>
       </c>
       <c r="F16">
-        <v>16.02998178345199</v>
+        <v>17.17498048226999</v>
       </c>
       <c r="G16">
         <v>2.92</v>
@@ -2599,28 +2599,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M16">
-        <v>0.8576040254146817</v>
+        <v>0.9188614558014446</v>
       </c>
       <c r="N16">
-        <v>6.752395974585317</v>
+        <v>6.691138544198555</v>
       </c>
       <c r="O16">
-        <v>2.025718792375595</v>
+        <v>2.007341563259566</v>
       </c>
       <c r="P16">
-        <v>4.726677182209722</v>
+        <v>4.683796980938989</v>
       </c>
       <c r="Q16">
-        <v>17.52667718220972</v>
+        <v>17.48379698093899</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07745370370535826</v>
+        <v>0.07772580971780763</v>
       </c>
       <c r="T16">
-        <v>0.7310324181376044</v>
+        <v>0.7373166216583747</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.87355909543486</v>
+        <v>8.281988489072539</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07168443826013647</v>
+        <v>0.07151569133366484</v>
       </c>
       <c r="C17">
-        <v>98.29020391713345</v>
+        <v>97.63690075390596</v>
       </c>
       <c r="D17">
-        <v>112.5451843994034</v>
+        <v>113.0368799349939</v>
       </c>
       <c r="E17">
-        <v>1.075110600470058</v>
+        <v>2.220109299288058</v>
       </c>
       <c r="F17">
-        <v>17.17498048226999</v>
+        <v>18.31997918108799</v>
       </c>
       <c r="G17">
         <v>2.92</v>
@@ -2681,28 +2681,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M17">
-        <v>0.9188614558014445</v>
+        <v>0.9801188861882075</v>
       </c>
       <c r="N17">
-        <v>6.691138544198555</v>
+        <v>6.629881113811792</v>
       </c>
       <c r="O17">
-        <v>2.007341563259566</v>
+        <v>1.988964334143537</v>
       </c>
       <c r="P17">
-        <v>4.683796980938989</v>
+        <v>4.640916779668254</v>
       </c>
       <c r="Q17">
-        <v>17.48379698093899</v>
+        <v>17.44091677966826</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07772580971780763</v>
+        <v>0.0780043944448391</v>
       </c>
       <c r="T17">
-        <v>0.7373166216583747</v>
+        <v>0.7437504490724967</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.281988489072539</v>
+        <v>7.764364208505506</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07151569133366484</v>
+        <v>0.07144214440719321</v>
       </c>
       <c r="C18">
-        <v>97.63690075390596</v>
+        <v>96.70755029137028</v>
       </c>
       <c r="D18">
-        <v>113.0368799349939</v>
+        <v>113.2525281712763</v>
       </c>
       <c r="E18">
-        <v>2.220109299288058</v>
+        <v>3.365107998106058</v>
       </c>
       <c r="F18">
-        <v>18.31997918108799</v>
+        <v>19.46497787990599</v>
       </c>
       <c r="G18">
         <v>2.92</v>
@@ -2763,45 +2763,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M18">
-        <v>0.9801188861882075</v>
+        <v>1.056948298878895</v>
       </c>
       <c r="N18">
-        <v>6.629881113811792</v>
+        <v>6.553051701121104</v>
       </c>
       <c r="O18">
-        <v>1.988964334143537</v>
+        <v>1.965915510336331</v>
       </c>
       <c r="P18">
-        <v>4.640916779668254</v>
+        <v>4.587136190784773</v>
       </c>
       <c r="Q18">
-        <v>17.44091677966826</v>
+        <v>17.38713619078477</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0780043944448391</v>
+        <v>0.07828969205685929</v>
       </c>
       <c r="T18">
-        <v>0.7437504490724967</v>
+        <v>0.7503393084725012</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.764364208505506</v>
+        <v>7.199973743343855</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07144214440719321</v>
+        <v>0.07127899748072157</v>
       </c>
       <c r="C19">
-        <v>96.70755029137028</v>
+        <v>96.04386707709996</v>
       </c>
       <c r="D19">
-        <v>113.2525281712763</v>
+        <v>113.7338436558239</v>
       </c>
       <c r="E19">
-        <v>3.365107998106058</v>
+        <v>4.510106696924058</v>
       </c>
       <c r="F19">
-        <v>19.46497787990599</v>
+        <v>20.60997657872399</v>
       </c>
       <c r="G19">
         <v>2.92</v>
@@ -2845,28 +2845,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M19">
-        <v>1.056948298878895</v>
+        <v>1.119121728224713</v>
       </c>
       <c r="N19">
-        <v>6.553051701121104</v>
+        <v>6.490878271775287</v>
       </c>
       <c r="O19">
-        <v>1.965915510336331</v>
+        <v>1.947263481532586</v>
       </c>
       <c r="P19">
-        <v>4.587136190784773</v>
+        <v>4.543614790242701</v>
       </c>
       <c r="Q19">
-        <v>17.38713619078477</v>
+        <v>17.3436147902427</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07828969205685929</v>
+        <v>0.07858194814722144</v>
       </c>
       <c r="T19">
-        <v>0.7503393084725012</v>
+        <v>0.7570888717603104</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.199973743343855</v>
+        <v>6.799975202046974</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07127899748072158</v>
+        <v>0.07111585055424996</v>
       </c>
       <c r="C20">
-        <v>96.0438670770999</v>
+        <v>95.38429243965776</v>
       </c>
       <c r="D20">
-        <v>113.7338436558239</v>
+        <v>114.2192677171997</v>
       </c>
       <c r="E20">
-        <v>4.510106696924055</v>
+        <v>5.655105395742055</v>
       </c>
       <c r="F20">
-        <v>20.60997657872399</v>
+        <v>21.75497527754199</v>
       </c>
       <c r="G20">
         <v>2.92</v>
@@ -2927,28 +2927,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M20">
-        <v>1.119121728224713</v>
+        <v>1.18129515757053</v>
       </c>
       <c r="N20">
-        <v>6.490878271775287</v>
+        <v>6.42870484242947</v>
       </c>
       <c r="O20">
-        <v>1.947263481532586</v>
+        <v>1.928611452728841</v>
       </c>
       <c r="P20">
-        <v>4.543614790242701</v>
+        <v>4.500093389700629</v>
       </c>
       <c r="Q20">
-        <v>17.3436147902427</v>
+        <v>17.30009338970063</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07858194814722144</v>
+        <v>0.07888142043734561</v>
       </c>
       <c r="T20">
-        <v>0.7570888717603104</v>
+        <v>0.7640050909317694</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.799975202046975</v>
+        <v>6.442081770360292</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07111585055424996</v>
+        <v>0.07095270362777832</v>
       </c>
       <c r="C21">
-        <v>95.38429243965776</v>
+        <v>94.72887921162345</v>
       </c>
       <c r="D21">
-        <v>114.2192677171997</v>
+        <v>114.7088531879834</v>
       </c>
       <c r="E21">
-        <v>5.655105395742055</v>
+        <v>6.800104094560055</v>
       </c>
       <c r="F21">
-        <v>21.75497527754199</v>
+        <v>22.89997397635999</v>
       </c>
       <c r="G21">
         <v>2.92</v>
@@ -3009,28 +3009,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M21">
-        <v>1.18129515757053</v>
+        <v>1.243468586916347</v>
       </c>
       <c r="N21">
-        <v>6.42870484242947</v>
+        <v>6.366531413083652</v>
       </c>
       <c r="O21">
-        <v>1.928611452728841</v>
+        <v>1.909959423925095</v>
       </c>
       <c r="P21">
-        <v>4.500093389700629</v>
+        <v>4.456571989158556</v>
       </c>
       <c r="Q21">
-        <v>17.30009338970063</v>
+        <v>17.25657198915856</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07888142043734561</v>
+        <v>0.07918837953472289</v>
       </c>
       <c r="T21">
-        <v>0.7640050909317694</v>
+        <v>0.771094215582515</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.442081770360292</v>
+        <v>6.119977681842277</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07095270362777832</v>
+        <v>0.07093655670130668</v>
       </c>
       <c r="C22">
-        <v>94.72887921162345</v>
+        <v>93.63256396173239</v>
       </c>
       <c r="D22">
-        <v>114.7088531879834</v>
+        <v>114.7575366369104</v>
       </c>
       <c r="E22">
-        <v>6.800104094560055</v>
+        <v>7.945102793378055</v>
       </c>
       <c r="F22">
-        <v>22.89997397635999</v>
+        <v>24.04497267517799</v>
       </c>
       <c r="G22">
         <v>2.92</v>
@@ -3091,45 +3091,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M22">
-        <v>1.243468586916347</v>
+        <v>1.329686988937343</v>
       </c>
       <c r="N22">
-        <v>6.366531413083652</v>
+        <v>6.280313011062656</v>
       </c>
       <c r="O22">
-        <v>1.909959423925095</v>
+        <v>1.884093903318797</v>
       </c>
       <c r="P22">
-        <v>4.456571989158556</v>
+        <v>4.396219107743859</v>
       </c>
       <c r="Q22">
-        <v>17.25657198915856</v>
+        <v>17.19621910774386</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07918837953472289</v>
+        <v>0.07950310974848947</v>
       </c>
       <c r="T22">
-        <v>0.771094215582515</v>
+        <v>0.7783628117434059</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.119977681842277</v>
+        <v>5.723151435874203</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07093655670130668</v>
+        <v>0.07078040977483505</v>
       </c>
       <c r="C23">
-        <v>93.63256396173239</v>
+        <v>92.96049354508719</v>
       </c>
       <c r="D23">
-        <v>114.7575366369104</v>
+        <v>115.2304649190832</v>
       </c>
       <c r="E23">
-        <v>7.945102793378055</v>
+        <v>9.090101492196055</v>
       </c>
       <c r="F23">
-        <v>24.04497267517799</v>
+        <v>25.18997137399599</v>
       </c>
       <c r="G23">
         <v>2.92</v>
@@ -3173,28 +3173,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M23">
-        <v>1.329686988937343</v>
+        <v>1.393005416981978</v>
       </c>
       <c r="N23">
-        <v>6.280313011062656</v>
+        <v>6.216994583018021</v>
       </c>
       <c r="O23">
-        <v>1.884093903318797</v>
+        <v>1.865098374905406</v>
       </c>
       <c r="P23">
-        <v>4.396219107743859</v>
+        <v>4.351896208112615</v>
       </c>
       <c r="Q23">
-        <v>17.19621910774386</v>
+        <v>17.15189620811262</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07950310974848947</v>
+        <v>0.07982590996773724</v>
       </c>
       <c r="T23">
-        <v>0.7783628117434058</v>
+        <v>0.7858177821648324</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.723151435874203</v>
+        <v>5.463008188789012</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07078040977483505</v>
+        <v>0.07062426284836341</v>
       </c>
       <c r="C24">
-        <v>92.96049354508719</v>
+        <v>92.29233723661979</v>
       </c>
       <c r="D24">
-        <v>115.2304649190832</v>
+        <v>115.7073073094338</v>
       </c>
       <c r="E24">
-        <v>9.090101492196055</v>
+        <v>10.23510019101406</v>
       </c>
       <c r="F24">
-        <v>25.18997137399599</v>
+        <v>26.33497007281399</v>
       </c>
       <c r="G24">
         <v>2.92</v>
@@ -3255,28 +3255,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M24">
-        <v>1.393005416981978</v>
+        <v>1.456323845026614</v>
       </c>
       <c r="N24">
-        <v>6.216994583018021</v>
+        <v>6.153676154973386</v>
       </c>
       <c r="O24">
-        <v>1.865098374905406</v>
+        <v>1.846102846492016</v>
       </c>
       <c r="P24">
-        <v>4.351896208112615</v>
+        <v>4.30757330848137</v>
       </c>
       <c r="Q24">
-        <v>17.15189620811262</v>
+        <v>17.10757330848137</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07982590996773724</v>
+        <v>0.08015709460826417</v>
       </c>
       <c r="T24">
-        <v>0.7858177821648324</v>
+        <v>0.7934663881816207</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.463008188789012</v>
+        <v>5.225486093624273</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07062426284836341</v>
+        <v>0.07046811592189178</v>
       </c>
       <c r="C25">
-        <v>92.29233723661979</v>
+        <v>91.62814382989306</v>
       </c>
       <c r="D25">
-        <v>115.7073073094338</v>
+        <v>116.188112601525</v>
       </c>
       <c r="E25">
-        <v>10.23510019101406</v>
+        <v>11.38009888983206</v>
       </c>
       <c r="F25">
-        <v>26.33497007281399</v>
+        <v>27.47996877163199</v>
       </c>
       <c r="G25">
         <v>2.92</v>
@@ -3337,28 +3337,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M25">
-        <v>1.456323845026614</v>
+        <v>1.519642273071249</v>
       </c>
       <c r="N25">
-        <v>6.153676154973386</v>
+        <v>6.090357726928751</v>
       </c>
       <c r="O25">
-        <v>1.846102846492016</v>
+        <v>1.827107318078625</v>
       </c>
       <c r="P25">
-        <v>4.30757330848137</v>
+        <v>4.263250408850126</v>
       </c>
       <c r="Q25">
-        <v>17.10757330848137</v>
+        <v>17.06325040885013</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08015709460826417</v>
+        <v>0.08049699463406813</v>
       </c>
       <c r="T25">
-        <v>0.7934663881816207</v>
+        <v>0.801316273304114</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.225486093624273</v>
+        <v>5.007757506389928</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07046811592189178</v>
+        <v>0.07031196899542015</v>
       </c>
       <c r="C26">
-        <v>91.62814382989306</v>
+        <v>90.96796293287299</v>
       </c>
       <c r="D26">
-        <v>116.188112601525</v>
+        <v>116.672930403323</v>
       </c>
       <c r="E26">
-        <v>11.38009888983205</v>
+        <v>12.52509758865005</v>
       </c>
       <c r="F26">
-        <v>27.47996877163198</v>
+        <v>28.62496747044998</v>
       </c>
       <c r="G26">
         <v>2.92</v>
@@ -3419,28 +3419,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M26">
-        <v>1.519642273071249</v>
+        <v>1.582960701115884</v>
       </c>
       <c r="N26">
-        <v>6.090357726928751</v>
+        <v>6.027039298884115</v>
       </c>
       <c r="O26">
-        <v>1.827107318078625</v>
+        <v>1.808111789665234</v>
       </c>
       <c r="P26">
-        <v>4.263250408850126</v>
+        <v>4.218927509218881</v>
       </c>
       <c r="Q26">
-        <v>17.06325040885013</v>
+        <v>17.01892750921888</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08049699463406813</v>
+        <v>0.0808459586605602</v>
       </c>
       <c r="T26">
-        <v>0.801316273304114</v>
+        <v>0.8093754886965405</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.007757506389928</v>
+        <v>4.807447206134331</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07031196899542015</v>
+        <v>0.07015582206894852</v>
       </c>
       <c r="C27">
-        <v>90.96796293287299</v>
+        <v>90.311844984991</v>
       </c>
       <c r="D27">
-        <v>116.672930403323</v>
+        <v>117.161811154259</v>
       </c>
       <c r="E27">
-        <v>12.52509758865005</v>
+        <v>13.67009628746805</v>
       </c>
       <c r="F27">
-        <v>28.62496747044998</v>
+        <v>29.76996616926798</v>
       </c>
       <c r="G27">
         <v>2.92</v>
@@ -3501,28 +3501,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M27">
-        <v>1.582960701115884</v>
+        <v>1.64627912916052</v>
       </c>
       <c r="N27">
-        <v>6.027039298884115</v>
+        <v>5.96372087083948</v>
       </c>
       <c r="O27">
-        <v>1.808111789665234</v>
+        <v>1.789116261251844</v>
       </c>
       <c r="P27">
-        <v>4.218927509218881</v>
+        <v>4.174604609587636</v>
       </c>
       <c r="Q27">
-        <v>17.01892750921888</v>
+        <v>16.97460460958764</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0808459586605602</v>
+        <v>0.08120435414722772</v>
       </c>
       <c r="T27">
-        <v>0.8093754886965405</v>
+        <v>0.8176525207211947</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.807447206134331</v>
+        <v>4.62254539051378</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07015582206894852</v>
+        <v>0.07047217514247689</v>
       </c>
       <c r="C28">
-        <v>90.311844984991</v>
+        <v>88.18059805928272</v>
       </c>
       <c r="D28">
-        <v>117.161811154259</v>
+        <v>116.1755629273687</v>
       </c>
       <c r="E28">
-        <v>13.67009628746805</v>
+        <v>14.81509498628605</v>
       </c>
       <c r="F28">
-        <v>29.76996616926798</v>
+        <v>30.91496486808598</v>
       </c>
       <c r="G28">
         <v>2.92</v>
@@ -3583,45 +3583,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M28">
-        <v>1.64627912916052</v>
+        <v>1.78688496937537</v>
       </c>
       <c r="N28">
-        <v>5.96372087083948</v>
+        <v>5.82311503062463</v>
       </c>
       <c r="O28">
-        <v>1.789116261251844</v>
+        <v>1.746934509187389</v>
       </c>
       <c r="P28">
-        <v>4.174604609587636</v>
+        <v>4.076180521437241</v>
       </c>
       <c r="Q28">
-        <v>16.97460460958764</v>
+        <v>16.87618052143724</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08120435414722772</v>
+        <v>0.08157256868832449</v>
       </c>
       <c r="T28">
-        <v>0.8176525207211947</v>
+        <v>0.8261563207465243</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.62254539051378</v>
+        <v>4.258807998513849</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07047217514247689</v>
+        <v>0.07033352821600525</v>
       </c>
       <c r="C29">
-        <v>88.18059805928272</v>
+        <v>87.46578738590811</v>
       </c>
       <c r="D29">
-        <v>116.1755629273687</v>
+        <v>116.6057509528121</v>
       </c>
       <c r="E29">
-        <v>14.81509498628605</v>
+        <v>15.96009368510406</v>
       </c>
       <c r="F29">
-        <v>30.91496486808598</v>
+        <v>32.05996356690399</v>
       </c>
       <c r="G29">
         <v>2.92</v>
@@ -3665,28 +3665,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M29">
-        <v>1.78688496937537</v>
+        <v>1.853065894167051</v>
       </c>
       <c r="N29">
-        <v>5.82311503062463</v>
+        <v>5.756934105832949</v>
       </c>
       <c r="O29">
-        <v>1.746934509187389</v>
+        <v>1.727080231749885</v>
       </c>
       <c r="P29">
-        <v>4.076180521437241</v>
+        <v>4.029853874083065</v>
       </c>
       <c r="Q29">
-        <v>16.87618052143724</v>
+        <v>16.82985387408306</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08157256868832449</v>
+        <v>0.08195101141111841</v>
       </c>
       <c r="T29">
-        <v>0.8261563207465243</v>
+        <v>0.8348963374392242</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.258807998513849</v>
+        <v>4.106707712852639</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07033352821600525</v>
+        <v>0.07090538128953361</v>
       </c>
       <c r="C30">
-        <v>87.46578738590811</v>
+        <v>84.56668614597081</v>
       </c>
       <c r="D30">
-        <v>116.6057509528121</v>
+        <v>114.8516484116928</v>
       </c>
       <c r="E30">
-        <v>15.96009368510406</v>
+        <v>17.10509238392206</v>
       </c>
       <c r="F30">
-        <v>32.05996356690399</v>
+        <v>33.20496226572199</v>
       </c>
       <c r="G30">
         <v>2.92</v>
@@ -3747,45 +3747,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M30">
-        <v>1.853065894167051</v>
+        <v>2.035464186888758</v>
       </c>
       <c r="N30">
-        <v>5.756934105832949</v>
+        <v>5.574535813111241</v>
       </c>
       <c r="O30">
-        <v>1.727080231749885</v>
+        <v>1.672360743933372</v>
       </c>
       <c r="P30">
-        <v>4.029853874083065</v>
+        <v>3.902175069177869</v>
       </c>
       <c r="Q30">
-        <v>16.82985387408306</v>
+        <v>16.70217506917787</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08195101141111841</v>
+        <v>0.08234011449230086</v>
       </c>
       <c r="T30">
-        <v>0.8348963374392242</v>
+        <v>0.8438825517852396</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.106707712852639</v>
+        <v>3.738704934736295</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07090538128953361</v>
+        <v>0.07079123436306198</v>
       </c>
       <c r="C31">
-        <v>84.56668614597081</v>
+        <v>83.76759339449478</v>
       </c>
       <c r="D31">
-        <v>114.8516484116928</v>
+        <v>115.1975543590348</v>
       </c>
       <c r="E31">
-        <v>17.10509238392205</v>
+        <v>18.25009108274005</v>
       </c>
       <c r="F31">
-        <v>33.20496226572198</v>
+        <v>34.34996096453998</v>
       </c>
       <c r="G31">
         <v>2.92</v>
@@ -3829,28 +3829,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M31">
-        <v>2.035464186888758</v>
+        <v>2.105652607126301</v>
       </c>
       <c r="N31">
-        <v>5.574535813111241</v>
+        <v>5.504347392873699</v>
       </c>
       <c r="O31">
-        <v>1.672360743933372</v>
+        <v>1.65130421786211</v>
       </c>
       <c r="P31">
-        <v>3.902175069177869</v>
+        <v>3.85304317501159</v>
       </c>
       <c r="Q31">
-        <v>16.70217506917787</v>
+        <v>16.65304317501159</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08234011449230086</v>
+        <v>0.08274033480437426</v>
       </c>
       <c r="T31">
-        <v>0.8438825517852396</v>
+        <v>0.8531255151125697</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.738704934736296</v>
+        <v>3.614081436911753</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07079123436306198</v>
+        <v>0.07128468743659035</v>
       </c>
       <c r="C32">
-        <v>83.76759339449478</v>
+        <v>81.14202866172221</v>
       </c>
       <c r="D32">
-        <v>115.1975543590348</v>
+        <v>113.7169883250802</v>
       </c>
       <c r="E32">
-        <v>18.25009108274005</v>
+        <v>19.39508978155805</v>
       </c>
       <c r="F32">
-        <v>34.34996096453998</v>
+        <v>35.49495966335798</v>
       </c>
       <c r="G32">
         <v>2.92</v>
@@ -3911,45 +3911,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M32">
-        <v>2.105652607126301</v>
+        <v>2.275226914421247</v>
       </c>
       <c r="N32">
-        <v>5.504347392873699</v>
+        <v>5.334773085578753</v>
       </c>
       <c r="O32">
-        <v>1.65130421786211</v>
+        <v>1.600431925673626</v>
       </c>
       <c r="P32">
-        <v>3.85304317501159</v>
+        <v>3.734341159905127</v>
       </c>
       <c r="Q32">
-        <v>16.65304317501159</v>
+        <v>16.53434115990513</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08274033480437426</v>
+        <v>0.0831521557052034</v>
       </c>
       <c r="T32">
-        <v>0.8531255151125697</v>
+        <v>0.8626363904204021</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.614081436911753</v>
+        <v>3.344721333843648</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07128468743659035</v>
+        <v>0.07119014051011871</v>
       </c>
       <c r="C33">
-        <v>81.14202866172221</v>
+        <v>80.27775569461991</v>
       </c>
       <c r="D33">
-        <v>113.7169883250802</v>
+        <v>113.9977140567959</v>
       </c>
       <c r="E33">
-        <v>19.39508978155805</v>
+        <v>20.54008848037605</v>
       </c>
       <c r="F33">
-        <v>35.49495966335798</v>
+        <v>36.63995836217598</v>
       </c>
       <c r="G33">
         <v>2.92</v>
@@ -3993,28 +3993,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M33">
-        <v>2.275226914421247</v>
+        <v>2.34862133101548</v>
       </c>
       <c r="N33">
-        <v>5.334773085578753</v>
+        <v>5.261378668984519</v>
       </c>
       <c r="O33">
-        <v>1.600431925673626</v>
+        <v>1.578413600695356</v>
       </c>
       <c r="P33">
-        <v>3.734341159905127</v>
+        <v>3.682965068289163</v>
       </c>
       <c r="Q33">
-        <v>16.53434115990513</v>
+        <v>16.48296506828916</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0831521557052034</v>
+        <v>0.0835760889854687</v>
       </c>
       <c r="T33">
-        <v>0.8626363904204021</v>
+        <v>0.8724269973549355</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.344721333843648</v>
+        <v>3.240198792161034</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07119014051011871</v>
+        <v>0.07109559358364707</v>
       </c>
       <c r="C34">
-        <v>80.27775569461991</v>
+        <v>79.41487217626434</v>
       </c>
       <c r="D34">
-        <v>113.9977140567959</v>
+        <v>114.2798292372583</v>
       </c>
       <c r="E34">
-        <v>20.54008848037605</v>
+        <v>21.68508717919405</v>
       </c>
       <c r="F34">
-        <v>36.63995836217598</v>
+        <v>37.78495706099398</v>
       </c>
       <c r="G34">
         <v>2.92</v>
@@ -4075,28 +4075,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M34">
-        <v>2.34862133101548</v>
+        <v>2.422015747609715</v>
       </c>
       <c r="N34">
-        <v>5.261378668984519</v>
+        <v>5.187984252390285</v>
       </c>
       <c r="O34">
-        <v>1.578413600695356</v>
+        <v>1.556395275717085</v>
       </c>
       <c r="P34">
-        <v>3.682965068289163</v>
+        <v>3.631588976673199</v>
       </c>
       <c r="Q34">
-        <v>16.48296506828916</v>
+        <v>16.4315889766732</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0835760889854687</v>
+        <v>0.08401267699051804</v>
       </c>
       <c r="T34">
-        <v>0.8724269973549355</v>
+        <v>0.882509861212888</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.240198792161034</v>
+        <v>3.142010949974335</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07109559358364707</v>
+        <v>0.07100104665717545</v>
       </c>
       <c r="C35">
-        <v>79.41487217626434</v>
+        <v>78.55338844783788</v>
       </c>
       <c r="D35">
-        <v>114.2798292372583</v>
+        <v>114.5633442076498</v>
       </c>
       <c r="E35">
-        <v>21.68508717919405</v>
+        <v>22.83008587801205</v>
       </c>
       <c r="F35">
-        <v>37.78495706099398</v>
+        <v>38.92995575981198</v>
       </c>
       <c r="G35">
         <v>2.92</v>
@@ -4157,28 +4157,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M35">
-        <v>2.422015747609715</v>
+        <v>2.495410164203948</v>
       </c>
       <c r="N35">
-        <v>5.187984252390285</v>
+        <v>5.114589835796052</v>
       </c>
       <c r="O35">
-        <v>1.556395275717085</v>
+        <v>1.534376950738815</v>
       </c>
       <c r="P35">
-        <v>3.631588976673199</v>
+        <v>3.580212885057236</v>
       </c>
       <c r="Q35">
-        <v>16.4315889766732</v>
+        <v>16.38021288505724</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08401267699051804</v>
+        <v>0.08446249493511432</v>
       </c>
       <c r="T35">
-        <v>0.882509861212888</v>
+        <v>0.892898266399869</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.142010949974335</v>
+        <v>3.049598863210385</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07100104665717545</v>
+        <v>0.07281749973070381</v>
       </c>
       <c r="C36">
-        <v>78.55338844783788</v>
+        <v>72.19635653664128</v>
       </c>
       <c r="D36">
-        <v>114.5633442076498</v>
+        <v>109.3513109952713</v>
       </c>
       <c r="E36">
-        <v>22.83008587801205</v>
+        <v>23.97508457683005</v>
       </c>
       <c r="F36">
-        <v>38.92995575981198</v>
+        <v>40.07495445862998</v>
       </c>
       <c r="G36">
         <v>2.92</v>
@@ -4239,45 +4239,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M36">
-        <v>2.495410164203948</v>
+        <v>2.881389225575496</v>
       </c>
       <c r="N36">
-        <v>5.114589835796052</v>
+        <v>4.728610774424503</v>
       </c>
       <c r="O36">
-        <v>1.534376950738815</v>
+        <v>1.418583232327351</v>
       </c>
       <c r="P36">
-        <v>3.580212885057236</v>
+        <v>3.310027542097152</v>
       </c>
       <c r="Q36">
-        <v>16.38021288505724</v>
+        <v>16.11002754209715</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08446249493511432</v>
+        <v>0.08492615343185203</v>
       </c>
       <c r="T36">
-        <v>0.892898266399869</v>
+        <v>0.9036063148233726</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.049598863210385</v>
+        <v>2.641087129934715</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07281749973070381</v>
+        <v>0.07277755280423218</v>
       </c>
       <c r="C37">
-        <v>72.19635653664128</v>
+        <v>71.16087430007047</v>
       </c>
       <c r="D37">
-        <v>109.3513109952713</v>
+        <v>109.4608274575185</v>
       </c>
       <c r="E37">
-        <v>23.97508457683005</v>
+        <v>25.12008327564805</v>
       </c>
       <c r="F37">
-        <v>40.07495445862998</v>
+        <v>41.21995315744798</v>
       </c>
       <c r="G37">
         <v>2.92</v>
@@ -4321,28 +4321,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M37">
-        <v>2.881389225575496</v>
+        <v>2.96371463202051</v>
       </c>
       <c r="N37">
-        <v>4.728610774424503</v>
+        <v>4.646285367979489</v>
       </c>
       <c r="O37">
-        <v>1.418583232327351</v>
+        <v>1.393885610393847</v>
       </c>
       <c r="P37">
-        <v>3.310027542097152</v>
+        <v>3.252399757585643</v>
       </c>
       <c r="Q37">
-        <v>16.11002754209715</v>
+        <v>16.05239975758564</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08492615343185203</v>
+        <v>0.08540430125661279</v>
       </c>
       <c r="T37">
-        <v>0.9036063148233726</v>
+        <v>0.9146489897601108</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.641087129934715</v>
+        <v>2.56772359854764</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07277755280423219</v>
+        <v>0.07374770587776056</v>
       </c>
       <c r="C38">
-        <v>71.16087430007046</v>
+        <v>67.41670837037752</v>
       </c>
       <c r="D38">
-        <v>109.4608274575184</v>
+        <v>106.8616602266435</v>
       </c>
       <c r="E38">
-        <v>25.12008327564804</v>
+        <v>26.26508197446604</v>
       </c>
       <c r="F38">
-        <v>41.21995315744797</v>
+        <v>42.36495185626598</v>
       </c>
       <c r="G38">
         <v>2.92</v>
@@ -4403,45 +4403,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M38">
-        <v>2.96371463202051</v>
+        <v>3.211263350704961</v>
       </c>
       <c r="N38">
-        <v>4.646285367979489</v>
+        <v>4.398736649295039</v>
       </c>
       <c r="O38">
-        <v>1.393885610393847</v>
+        <v>1.319620994788512</v>
       </c>
       <c r="P38">
-        <v>3.252399757585643</v>
+        <v>3.079115654506527</v>
       </c>
       <c r="Q38">
-        <v>16.05239975758564</v>
+        <v>15.87911565450653</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08540430125661279</v>
+        <v>0.0858976283773977</v>
       </c>
       <c r="T38">
-        <v>0.9146489897601108</v>
+        <v>0.9260422258059516</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.56772359854764</v>
+        <v>2.369783841717433</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07374770587776056</v>
+        <v>0.07373505895128891</v>
       </c>
       <c r="C39">
-        <v>67.41670837037752</v>
+        <v>66.30479813473808</v>
       </c>
       <c r="D39">
-        <v>106.8616602266435</v>
+        <v>106.8947486898221</v>
       </c>
       <c r="E39">
-        <v>26.26508197446604</v>
+        <v>27.41008067328404</v>
       </c>
       <c r="F39">
-        <v>42.36495185626598</v>
+        <v>43.50995055508398</v>
       </c>
       <c r="G39">
         <v>2.92</v>
@@ -4485,28 +4485,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M39">
-        <v>3.211263350704961</v>
+        <v>3.298054252075366</v>
       </c>
       <c r="N39">
-        <v>4.398736649295039</v>
+        <v>4.311945747924634</v>
       </c>
       <c r="O39">
-        <v>1.319620994788512</v>
+        <v>1.29358372437739</v>
       </c>
       <c r="P39">
-        <v>3.079115654506527</v>
+        <v>3.018362023547244</v>
       </c>
       <c r="Q39">
-        <v>15.87911565450653</v>
+        <v>15.81836202354724</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0858976283773977</v>
+        <v>0.08640686927627245</v>
       </c>
       <c r="T39">
-        <v>0.9260422258059516</v>
+        <v>0.9378029855952068</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.369783841717433</v>
+        <v>2.307421109040658</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07373505895128891</v>
+        <v>0.07372241202481729</v>
       </c>
       <c r="C40">
-        <v>66.30479813473808</v>
+        <v>65.19290839635654</v>
       </c>
       <c r="D40">
-        <v>106.8947486898221</v>
+        <v>106.9278576502585</v>
       </c>
       <c r="E40">
-        <v>27.41008067328404</v>
+        <v>28.55507937210204</v>
       </c>
       <c r="F40">
-        <v>43.50995055508398</v>
+        <v>44.65494925390198</v>
       </c>
       <c r="G40">
         <v>2.92</v>
@@ -4567,28 +4567,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M40">
-        <v>3.298054252075366</v>
+        <v>3.38484515344577</v>
       </c>
       <c r="N40">
-        <v>4.311945747924634</v>
+        <v>4.225154846554229</v>
       </c>
       <c r="O40">
-        <v>1.29358372437739</v>
+        <v>1.267546453966269</v>
       </c>
       <c r="P40">
-        <v>3.018362023547244</v>
+        <v>2.957608392587961</v>
       </c>
       <c r="Q40">
-        <v>15.81836202354724</v>
+        <v>15.75760839258796</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08640686927627245</v>
+        <v>0.08693280659806113</v>
       </c>
       <c r="T40">
-        <v>0.9378029855952068</v>
+        <v>0.949949344066077</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.307421109040658</v>
+        <v>2.248256465219103</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07372241202481729</v>
+        <v>0.07370976509834566</v>
       </c>
       <c r="C41">
-        <v>65.19290839635654</v>
+        <v>64.08103917428497</v>
       </c>
       <c r="D41">
-        <v>106.9278576502585</v>
+        <v>106.9609871270049</v>
       </c>
       <c r="E41">
-        <v>28.55507937210204</v>
+        <v>29.70007807092004</v>
       </c>
       <c r="F41">
-        <v>44.65494925390198</v>
+        <v>45.79994795271998</v>
       </c>
       <c r="G41">
         <v>2.92</v>
@@ -4649,28 +4649,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M41">
-        <v>3.38484515344577</v>
+        <v>3.471636054816174</v>
       </c>
       <c r="N41">
-        <v>4.225154846554229</v>
+        <v>4.138363945183825</v>
       </c>
       <c r="O41">
-        <v>1.267546453966269</v>
+        <v>1.241509183555147</v>
       </c>
       <c r="P41">
-        <v>2.957608392587961</v>
+        <v>2.896854761628677</v>
       </c>
       <c r="Q41">
-        <v>15.75760839258796</v>
+        <v>15.69685476162868</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08693280659806113</v>
+        <v>0.08747627516390943</v>
       </c>
       <c r="T41">
-        <v>0.949949344066077</v>
+        <v>0.9625005811526428</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.248256465219103</v>
+        <v>2.192050053588625</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07370976509834566</v>
+        <v>0.07369711817187402</v>
       </c>
       <c r="C42">
-        <v>64.08103917428497</v>
+        <v>62.96919048759899</v>
       </c>
       <c r="D42">
-        <v>106.9609871270049</v>
+        <v>106.994137139137</v>
       </c>
       <c r="E42">
-        <v>29.70007807092004</v>
+        <v>30.84507676973804</v>
       </c>
       <c r="F42">
-        <v>45.79994795271998</v>
+        <v>46.94494665153798</v>
       </c>
       <c r="G42">
         <v>2.92</v>
@@ -4731,28 +4731,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M42">
-        <v>3.471636054816174</v>
+        <v>3.558426956186579</v>
       </c>
       <c r="N42">
-        <v>4.138363945183825</v>
+        <v>4.051573043813421</v>
       </c>
       <c r="O42">
-        <v>1.241509183555147</v>
+        <v>1.215471913144026</v>
       </c>
       <c r="P42">
-        <v>2.896854761628677</v>
+        <v>2.836101130669395</v>
       </c>
       <c r="Q42">
-        <v>15.69685476162868</v>
+        <v>15.6361011306694</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08747627516390943</v>
+        <v>0.08803816639300682</v>
       </c>
       <c r="T42">
-        <v>0.9625005811526428</v>
+        <v>0.9754772839031599</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.192050053588625</v>
+        <v>2.138585418135245</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07369711817187402</v>
+        <v>0.07368447124540239</v>
       </c>
       <c r="C43">
-        <v>62.96919048759899</v>
+        <v>61.85736235539783</v>
       </c>
       <c r="D43">
-        <v>106.994137139137</v>
+        <v>107.0273077057538</v>
       </c>
       <c r="E43">
-        <v>30.84507676973804</v>
+        <v>31.99007546855604</v>
       </c>
       <c r="F43">
-        <v>46.94494665153798</v>
+        <v>48.08994535035598</v>
       </c>
       <c r="G43">
         <v>2.92</v>
@@ -4813,28 +4813,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M43">
-        <v>3.558426956186579</v>
+        <v>3.645217857556983</v>
       </c>
       <c r="N43">
-        <v>4.051573043813421</v>
+        <v>3.964782142443016</v>
       </c>
       <c r="O43">
-        <v>1.215471913144026</v>
+        <v>1.189434642732905</v>
       </c>
       <c r="P43">
-        <v>2.836101130669395</v>
+        <v>2.775347499710112</v>
       </c>
       <c r="Q43">
-        <v>15.6361011306694</v>
+        <v>15.57534749971011</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08803816639300682</v>
+        <v>0.08861943318172825</v>
       </c>
       <c r="T43">
-        <v>0.9754772839031599</v>
+        <v>0.9889014591623155</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.138585418135245</v>
+        <v>2.087666717703453</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07368447124540239</v>
+        <v>0.07367182431893077</v>
       </c>
       <c r="C44">
-        <v>61.85736235539783</v>
+        <v>60.74555479680451</v>
       </c>
       <c r="D44">
-        <v>107.0273077057538</v>
+        <v>107.0604988459785</v>
       </c>
       <c r="E44">
-        <v>31.99007546855604</v>
+        <v>33.13507416737404</v>
       </c>
       <c r="F44">
-        <v>48.08994535035598</v>
+        <v>49.23494404917398</v>
       </c>
       <c r="G44">
         <v>2.92</v>
@@ -4895,28 +4895,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M44">
-        <v>3.645217857556983</v>
+        <v>3.732008758927388</v>
       </c>
       <c r="N44">
-        <v>3.964782142443016</v>
+        <v>3.877991241072612</v>
       </c>
       <c r="O44">
-        <v>1.189434642732905</v>
+        <v>1.163397372321783</v>
       </c>
       <c r="P44">
-        <v>2.775347499710112</v>
+        <v>2.714593868750828</v>
       </c>
       <c r="Q44">
-        <v>15.57534749971011</v>
+        <v>15.51459386875083</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08861943318172824</v>
+        <v>0.08922109529636975</v>
       </c>
       <c r="T44">
-        <v>0.9889014591623154</v>
+        <v>1.002796658114775</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.087666717703453</v>
+        <v>2.039116328919651</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07367182431893077</v>
+        <v>0.07803277739245912</v>
       </c>
       <c r="C45">
-        <v>60.74555479680451</v>
+        <v>49.25793209772374</v>
       </c>
       <c r="D45">
-        <v>107.0604988459785</v>
+        <v>96.71787484571571</v>
       </c>
       <c r="E45">
-        <v>33.13507416737404</v>
+        <v>34.28007286619204</v>
       </c>
       <c r="F45">
-        <v>49.23494404917398</v>
+        <v>50.37994274799198</v>
       </c>
       <c r="G45">
         <v>2.92</v>
@@ -4977,45 +4977,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M45">
-        <v>3.732008758927388</v>
+        <v>4.534194847319277</v>
       </c>
       <c r="N45">
-        <v>3.877991241072612</v>
+        <v>3.075805152680722</v>
       </c>
       <c r="O45">
-        <v>1.163397372321783</v>
+        <v>0.9227415458042166</v>
       </c>
       <c r="P45">
-        <v>2.714593868750828</v>
+        <v>2.153063606876505</v>
       </c>
       <c r="Q45">
-        <v>15.51459386875083</v>
+        <v>14.95306360687651</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08922109529636975</v>
+        <v>0.08984424534367699</v>
       </c>
       <c r="T45">
-        <v>1.002796658114775</v>
+        <v>1.017188114172679</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.039116328919651</v>
+        <v>1.678357515777958</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07803277739245912</v>
+        <v>0.07811953046598749</v>
       </c>
       <c r="C46">
-        <v>49.25793209772374</v>
+        <v>47.9274189007179</v>
       </c>
       <c r="D46">
-        <v>96.71787484571571</v>
+        <v>96.53236034752787</v>
       </c>
       <c r="E46">
-        <v>34.28007286619204</v>
+        <v>35.42507156501004</v>
       </c>
       <c r="F46">
-        <v>50.37994274799198</v>
+        <v>51.52494144680998</v>
       </c>
       <c r="G46">
         <v>2.92</v>
@@ -5059,28 +5059,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M46">
-        <v>4.534194847319277</v>
+        <v>4.637244730212898</v>
       </c>
       <c r="N46">
-        <v>3.075805152680722</v>
+        <v>2.972755269787101</v>
       </c>
       <c r="O46">
-        <v>0.9227415458042166</v>
+        <v>0.8918265809361304</v>
       </c>
       <c r="P46">
-        <v>2.153063606876505</v>
+        <v>2.080928688850971</v>
       </c>
       <c r="Q46">
-        <v>14.95306360687651</v>
+        <v>14.88092868885097</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08984424534367699</v>
+        <v>0.09049005539270452</v>
       </c>
       <c r="T46">
-        <v>1.017188114172679</v>
+        <v>1.032102895905417</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.678357515777958</v>
+        <v>1.641060682094003</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07811953046598749</v>
+        <v>0.07820628353951586</v>
       </c>
       <c r="C47">
-        <v>47.9274189007179</v>
+        <v>46.59761601176776</v>
       </c>
       <c r="D47">
-        <v>96.53236034752787</v>
+        <v>96.34755615739573</v>
       </c>
       <c r="E47">
-        <v>35.42507156501004</v>
+        <v>36.57007026382804</v>
       </c>
       <c r="F47">
-        <v>51.52494144680998</v>
+        <v>52.66994014562798</v>
       </c>
       <c r="G47">
         <v>2.92</v>
@@ -5141,28 +5141,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M47">
-        <v>4.637244730212898</v>
+        <v>4.740294613106518</v>
       </c>
       <c r="N47">
-        <v>2.972755269787101</v>
+        <v>2.869705386893481</v>
       </c>
       <c r="O47">
-        <v>0.8918265809361304</v>
+        <v>0.8609116160680444</v>
       </c>
       <c r="P47">
-        <v>2.080928688850971</v>
+        <v>2.008793770825437</v>
       </c>
       <c r="Q47">
-        <v>14.88092868885097</v>
+        <v>14.80879377082544</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09049005539270452</v>
+        <v>0.09115978433243677</v>
       </c>
       <c r="T47">
-        <v>1.032102895905417</v>
+        <v>1.047570076961588</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.641060682094003</v>
+        <v>1.605385449874568</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07820628353951586</v>
+        <v>0.07829303661304422</v>
       </c>
       <c r="C48">
-        <v>46.59761601176776</v>
+        <v>45.26851935916885</v>
       </c>
       <c r="D48">
-        <v>96.34755615739573</v>
+        <v>96.16345820361482</v>
       </c>
       <c r="E48">
-        <v>36.57007026382804</v>
+        <v>37.71506896264604</v>
       </c>
       <c r="F48">
-        <v>52.66994014562798</v>
+        <v>53.81493884444598</v>
       </c>
       <c r="G48">
         <v>2.92</v>
@@ -5223,28 +5223,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M48">
-        <v>4.740294613106518</v>
+        <v>4.843344496000138</v>
       </c>
       <c r="N48">
-        <v>2.869705386893481</v>
+        <v>2.766655503999861</v>
       </c>
       <c r="O48">
-        <v>0.8609116160680444</v>
+        <v>0.8299966511999585</v>
       </c>
       <c r="P48">
-        <v>2.008793770825437</v>
+        <v>1.936658852799903</v>
       </c>
       <c r="Q48">
-        <v>14.80879377082544</v>
+        <v>14.7366588527999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09115978433243677</v>
+        <v>0.09185478606234759</v>
       </c>
       <c r="T48">
-        <v>1.047570076961588</v>
+        <v>1.063620925227427</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.605385449874568</v>
+        <v>1.571228312643195</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07829303661304422</v>
+        <v>0.0783797896865726</v>
       </c>
       <c r="C49">
-        <v>45.26851935916885</v>
+        <v>43.94012490227757</v>
       </c>
       <c r="D49">
-        <v>96.16345820361482</v>
+        <v>95.98006244554155</v>
       </c>
       <c r="E49">
-        <v>37.71506896264604</v>
+        <v>38.86006766146404</v>
       </c>
       <c r="F49">
-        <v>53.81493884444598</v>
+        <v>54.95993754326398</v>
       </c>
       <c r="G49">
         <v>2.92</v>
@@ -5305,28 +5305,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M49">
-        <v>4.843344496000138</v>
+        <v>4.946394378893758</v>
       </c>
       <c r="N49">
-        <v>2.766655503999861</v>
+        <v>2.663605621106242</v>
       </c>
       <c r="O49">
-        <v>0.8299966511999585</v>
+        <v>0.7990816863318725</v>
       </c>
       <c r="P49">
-        <v>1.936658852799903</v>
+        <v>1.864523934774369</v>
       </c>
       <c r="Q49">
-        <v>14.7366588527999</v>
+        <v>14.66452393477437</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09185478606234759</v>
+        <v>0.09257651862802421</v>
       </c>
       <c r="T49">
-        <v>1.063620925227427</v>
+        <v>1.080289113811183</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.571228312643195</v>
+        <v>1.538494389463128</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0783797896865726</v>
+        <v>0.07846654276010095</v>
       </c>
       <c r="C50">
-        <v>43.94012490227758</v>
+        <v>42.61242863121591</v>
       </c>
       <c r="D50">
-        <v>95.98006244554155</v>
+        <v>95.79736487329788</v>
       </c>
       <c r="E50">
-        <v>38.86006766146404</v>
+        <v>40.00506636028204</v>
       </c>
       <c r="F50">
-        <v>54.95993754326397</v>
+        <v>56.10493624208197</v>
       </c>
       <c r="G50">
         <v>2.92</v>
@@ -5387,28 +5387,28 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M50">
-        <v>4.946394378893757</v>
+        <v>5.049444261787377</v>
       </c>
       <c r="N50">
-        <v>2.663605621106242</v>
+        <v>2.560555738212623</v>
       </c>
       <c r="O50">
-        <v>0.7990816863318727</v>
+        <v>0.7681667214637867</v>
       </c>
       <c r="P50">
-        <v>1.86452393477437</v>
+        <v>1.792389016748836</v>
       </c>
       <c r="Q50">
-        <v>14.66452393477437</v>
+        <v>14.59238901674884</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09257651862802421</v>
+        <v>0.09332655443157051</v>
       </c>
       <c r="T50">
-        <v>1.080289113811183</v>
+        <v>1.097610956849203</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.538494389463128</v>
+        <v>1.507096544780207</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07846654276010095</v>
+        <v>0.1009172433835773</v>
       </c>
       <c r="C51">
-        <v>42.61242863121591</v>
+        <v>9.85148834702688</v>
       </c>
       <c r="D51">
-        <v>95.79736487329788</v>
+        <v>64.18142328792685</v>
       </c>
       <c r="E51">
-        <v>40.00506636028204</v>
+        <v>41.15006505910004</v>
       </c>
       <c r="F51">
-        <v>56.10493624208197</v>
+        <v>57.24993494089997</v>
       </c>
       <c r="G51">
         <v>2.92</v>
@@ -5469,45 +5469,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M51">
-        <v>5.049444261787377</v>
+        <v>8.404290449324117</v>
       </c>
       <c r="N51">
-        <v>2.560555738212623</v>
+        <v>-0.7942904493241176</v>
       </c>
       <c r="O51">
-        <v>0.7681667214637867</v>
+        <v>-0.2382871347972353</v>
       </c>
       <c r="P51">
-        <v>1.792389016748836</v>
+        <v>-0.5560033145268823</v>
       </c>
       <c r="Q51">
-        <v>14.59238901674884</v>
+        <v>12.24399668547312</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09332655443157051</v>
+        <v>0.09491226134203885</v>
       </c>
       <c r="T51">
-        <v>1.097610956849203</v>
+        <v>1.13423236355748</v>
       </c>
       <c r="U51">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.3</v>
+        <v>0.2716469657689664</v>
       </c>
       <c r="W51">
-        <v>0.063</v>
+        <v>0.1069222254251157</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.507096544780207</v>
+        <v>0.9054898858965548</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1009172433835773</v>
+        <v>0.1019272433835773</v>
       </c>
       <c r="C52">
-        <v>9.85148834702688</v>
+        <v>7.76751746566827</v>
       </c>
       <c r="D52">
-        <v>64.18142328792685</v>
+        <v>63.24245110538624</v>
       </c>
       <c r="E52">
-        <v>41.15006505910004</v>
+        <v>42.29506375791804</v>
       </c>
       <c r="F52">
-        <v>57.24993494089997</v>
+        <v>58.39493363971797</v>
       </c>
       <c r="G52">
         <v>2.92</v>
@@ -5551,37 +5551,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M52">
-        <v>8.404290449324117</v>
+        <v>8.572376258310598</v>
       </c>
       <c r="N52">
-        <v>-0.7942904493241176</v>
+        <v>-0.9623762583105986</v>
       </c>
       <c r="O52">
-        <v>-0.2382871347972353</v>
+        <v>-0.2887128774931796</v>
       </c>
       <c r="P52">
-        <v>-0.5560033145268823</v>
+        <v>-0.6736633808174191</v>
       </c>
       <c r="Q52">
-        <v>12.24399668547312</v>
+        <v>12.12633661918258</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09491226134203885</v>
+        <v>0.09591455238983557</v>
       </c>
       <c r="T52">
-        <v>1.13423236355748</v>
+        <v>1.157379962813755</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2716469657689664</v>
+        <v>0.2663205546754573</v>
       </c>
       <c r="W52">
-        <v>0.1069222254251157</v>
+        <v>0.1077041425736429</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9054898858965548</v>
+        <v>0.8877351822515244</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1019272433835773</v>
+        <v>0.1029372433835773</v>
       </c>
       <c r="C53">
-        <v>7.76751746566827</v>
+        <v>5.710624698722718</v>
       </c>
       <c r="D53">
-        <v>63.24245110538624</v>
+        <v>62.33055703725869</v>
       </c>
       <c r="E53">
-        <v>42.29506375791804</v>
+        <v>43.44006245673604</v>
       </c>
       <c r="F53">
-        <v>58.39493363971797</v>
+        <v>59.53993233853597</v>
       </c>
       <c r="G53">
         <v>2.92</v>
@@ -5633,37 +5633,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M53">
-        <v>8.572376258310598</v>
+        <v>8.740462067297081</v>
       </c>
       <c r="N53">
-        <v>-0.9623762583105986</v>
+        <v>-1.130462067297081</v>
       </c>
       <c r="O53">
-        <v>-0.2887128774931796</v>
+        <v>-0.3391386201891244</v>
       </c>
       <c r="P53">
-        <v>-0.6736633808174191</v>
+        <v>-0.7913234471079569</v>
       </c>
       <c r="Q53">
-        <v>12.12633661918258</v>
+        <v>12.00867655289204</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09591455238983557</v>
+        <v>0.09695860556462381</v>
       </c>
       <c r="T53">
-        <v>1.157379962813755</v>
+        <v>1.181492045372375</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2663205546754573</v>
+        <v>0.2611990055470831</v>
       </c>
       <c r="W53">
-        <v>0.1077041425736429</v>
+        <v>0.1084559859856882</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8877351822515244</v>
+        <v>0.8706633518236104</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1029372433835773</v>
+        <v>0.1039472433835773</v>
       </c>
       <c r="C54">
-        <v>5.710624698722718</v>
+        <v>3.679655375909782</v>
       </c>
       <c r="D54">
-        <v>62.33055703725869</v>
+        <v>61.44458641326376</v>
       </c>
       <c r="E54">
-        <v>43.44006245673604</v>
+        <v>44.58506115555404</v>
       </c>
       <c r="F54">
-        <v>59.53993233853597</v>
+        <v>60.68493103735397</v>
       </c>
       <c r="G54">
         <v>2.92</v>
@@ -5715,37 +5715,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M54">
-        <v>8.740462067297081</v>
+        <v>8.908547876283563</v>
       </c>
       <c r="N54">
-        <v>-1.130462067297081</v>
+        <v>-1.298547876283564</v>
       </c>
       <c r="O54">
-        <v>-0.3391386201891244</v>
+        <v>-0.3895643628850692</v>
       </c>
       <c r="P54">
-        <v>-0.7913234471079569</v>
+        <v>-0.9089835133984949</v>
       </c>
       <c r="Q54">
-        <v>12.00867655289204</v>
+        <v>11.89101648660151</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09695860556462381</v>
+        <v>0.09804708653408389</v>
       </c>
       <c r="T54">
-        <v>1.181492045372375</v>
+        <v>1.206630173997319</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2611990055470831</v>
+        <v>0.2562707224235532</v>
       </c>
       <c r="W54">
-        <v>0.1084559859856882</v>
+        <v>0.1091794579482224</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8706633518236104</v>
+        <v>0.8542357414118441</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1039472433835773</v>
+        <v>0.1049572433835773</v>
       </c>
       <c r="C55">
-        <v>3.679655375909782</v>
+        <v>1.673519557106708</v>
       </c>
       <c r="D55">
-        <v>61.44458641326376</v>
+        <v>60.58344929327868</v>
       </c>
       <c r="E55">
-        <v>44.58506115555404</v>
+        <v>45.73005985437204</v>
       </c>
       <c r="F55">
-        <v>60.68493103735397</v>
+        <v>61.82992973617197</v>
       </c>
       <c r="G55">
         <v>2.92</v>
@@ -5797,37 +5797,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M55">
-        <v>8.908547876283563</v>
+        <v>9.076633685270046</v>
       </c>
       <c r="N55">
-        <v>-1.298547876283564</v>
+        <v>-1.466633685270047</v>
       </c>
       <c r="O55">
-        <v>-0.3895643628850692</v>
+        <v>-0.439990105581014</v>
       </c>
       <c r="P55">
-        <v>-0.9089835133984949</v>
+        <v>-1.026643579689033</v>
       </c>
       <c r="Q55">
-        <v>11.89101648660151</v>
+        <v>11.77335642031097</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09804708653408389</v>
+        <v>0.09918289276308571</v>
       </c>
       <c r="T55">
-        <v>1.206630173997319</v>
+        <v>1.232861264736391</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2562707224235532</v>
+        <v>0.2515249683045985</v>
       </c>
       <c r="W55">
-        <v>0.1091794579482224</v>
+        <v>0.1098761346528849</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8542357414118441</v>
+        <v>0.8384165610153285</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1049572433835773</v>
+        <v>0.1059672433835773</v>
       </c>
       <c r="C56">
-        <v>1.673519557106708</v>
+        <v>-0.3088124408797839</v>
       </c>
       <c r="D56">
-        <v>60.58344929327868</v>
+        <v>59.74611599411018</v>
       </c>
       <c r="E56">
-        <v>45.73005985437204</v>
+        <v>46.87505855319004</v>
       </c>
       <c r="F56">
-        <v>61.82992973617197</v>
+        <v>62.97492843498997</v>
       </c>
       <c r="G56">
         <v>2.92</v>
@@ -5879,37 +5879,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M56">
-        <v>9.076633685270046</v>
+        <v>9.244719494256529</v>
       </c>
       <c r="N56">
-        <v>-1.466633685270047</v>
+        <v>-1.63471949425653</v>
       </c>
       <c r="O56">
-        <v>-0.439990105581014</v>
+        <v>-0.4904158482769588</v>
       </c>
       <c r="P56">
-        <v>-1.026643579689033</v>
+        <v>-1.144303645979571</v>
       </c>
       <c r="Q56">
-        <v>11.77335642031097</v>
+        <v>11.65569635402043</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09918289276308571</v>
+        <v>0.1003691792689321</v>
       </c>
       <c r="T56">
-        <v>1.232861264736391</v>
+        <v>1.260258181730533</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2515249683045985</v>
+        <v>0.2469517870626967</v>
       </c>
       <c r="W56">
-        <v>0.1098761346528849</v>
+        <v>0.1105474776591961</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8384165610153285</v>
+        <v>0.8231726235423225</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1059672433835773</v>
+        <v>0.1069772433835773</v>
       </c>
       <c r="C57">
-        <v>-0.3088124408797839</v>
+        <v>-2.268314151647466</v>
       </c>
       <c r="D57">
-        <v>59.74611599411018</v>
+        <v>58.93161298216051</v>
       </c>
       <c r="E57">
-        <v>46.87505855319004</v>
+        <v>48.02005725200804</v>
       </c>
       <c r="F57">
-        <v>62.97492843498997</v>
+        <v>64.11992713380798</v>
       </c>
       <c r="G57">
         <v>2.92</v>
@@ -5961,37 +5961,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M57">
-        <v>9.244719494256529</v>
+        <v>9.412805303243012</v>
       </c>
       <c r="N57">
-        <v>-1.63471949425653</v>
+        <v>-1.802805303243012</v>
       </c>
       <c r="O57">
-        <v>-0.4904158482769588</v>
+        <v>-0.5408415909729036</v>
       </c>
       <c r="P57">
-        <v>-1.144303645979571</v>
+        <v>-1.261963712270109</v>
       </c>
       <c r="Q57">
-        <v>11.65569635402043</v>
+        <v>11.53803628772989</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1003691792689321</v>
+        <v>0.1016093878886805</v>
       </c>
       <c r="T57">
-        <v>1.260258181730533</v>
+        <v>1.2889004131335</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2469517870626967</v>
+        <v>0.2425419337222914</v>
       </c>
       <c r="W57">
-        <v>0.1105474776591961</v>
+        <v>0.1111948441295676</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8231726235423225</v>
+        <v>0.8084731124076381</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1069772433835773</v>
+        <v>0.1398051598191069</v>
       </c>
       <c r="C58">
-        <v>-2.268314151647466</v>
+        <v>-21.50819993700534</v>
       </c>
       <c r="D58">
-        <v>58.93161298216051</v>
+        <v>40.83672589562063</v>
       </c>
       <c r="E58">
-        <v>48.02005725200804</v>
+        <v>49.16505595082604</v>
       </c>
       <c r="F58">
-        <v>64.11992713380798</v>
+        <v>65.26492583262598</v>
       </c>
       <c r="G58">
         <v>2.92</v>
@@ -6043,45 +6043,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M58">
-        <v>9.412805303243012</v>
+        <v>13.1051971071913</v>
       </c>
       <c r="N58">
-        <v>-1.802805303243012</v>
+        <v>-5.495197107191297</v>
       </c>
       <c r="O58">
-        <v>-0.5408415909729036</v>
+        <v>-1.648559132157389</v>
       </c>
       <c r="P58">
-        <v>-1.261963712270109</v>
+        <v>-3.846637975033908</v>
       </c>
       <c r="Q58">
-        <v>11.53803628772989</v>
+        <v>8.953362024966093</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1016093878886805</v>
+        <v>0.1053210397826722</v>
       </c>
       <c r="T58">
-        <v>1.2889004131335</v>
+        <v>1.374619856412752</v>
       </c>
       <c r="U58">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.2425419337222914</v>
+        <v>0.1742056972761772</v>
       </c>
       <c r="W58">
-        <v>0.1111948441295676</v>
+        <v>0.1658194959869436</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8084731124076381</v>
+        <v>0.5806856575872572</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1398051598191069</v>
+        <v>0.1413551598191069</v>
       </c>
       <c r="C59">
-        <v>-21.50819993700534</v>
+        <v>-23.23677248463648</v>
       </c>
       <c r="D59">
-        <v>40.83672589562063</v>
+        <v>40.2531520468075</v>
       </c>
       <c r="E59">
-        <v>49.16505595082604</v>
+        <v>50.31005464964404</v>
       </c>
       <c r="F59">
-        <v>65.26492583262598</v>
+        <v>66.40992453144398</v>
       </c>
       <c r="G59">
         <v>2.92</v>
@@ -6125,37 +6125,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M59">
-        <v>13.1051971071913</v>
+        <v>13.33511284591395</v>
       </c>
       <c r="N59">
-        <v>-5.495197107191297</v>
+        <v>-5.725112845913952</v>
       </c>
       <c r="O59">
-        <v>-1.648559132157389</v>
+        <v>-1.717533853774185</v>
       </c>
       <c r="P59">
-        <v>-3.846637975033908</v>
+        <v>-4.007578992139766</v>
       </c>
       <c r="Q59">
-        <v>8.953362024966093</v>
+        <v>8.792421007860234</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1053210397826722</v>
+        <v>0.1067382073965453</v>
       </c>
       <c r="T59">
-        <v>1.374619856412752</v>
+        <v>1.407348900613056</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1742056972761772</v>
+        <v>0.1712021507714155</v>
       </c>
       <c r="W59">
-        <v>0.1658194959869436</v>
+        <v>0.1664226081250998</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5806856575872572</v>
+        <v>0.5706738359047183</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1413551598191069</v>
+        <v>0.1429051598191069</v>
       </c>
       <c r="C60">
-        <v>-23.23677248463645</v>
+        <v>-24.9489009968975</v>
       </c>
       <c r="D60">
-        <v>40.25315204680751</v>
+        <v>39.68602223336446</v>
       </c>
       <c r="E60">
-        <v>50.31005464964403</v>
+        <v>51.45505334846203</v>
       </c>
       <c r="F60">
-        <v>66.40992453144396</v>
+        <v>67.55492323026196</v>
       </c>
       <c r="G60">
         <v>2.92</v>
@@ -6207,37 +6207,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M60">
-        <v>13.33511284591395</v>
+        <v>13.5650285846366</v>
       </c>
       <c r="N60">
-        <v>-5.725112845913948</v>
+        <v>-5.955028584636603</v>
       </c>
       <c r="O60">
-        <v>-1.717533853774184</v>
+        <v>-1.786508575390981</v>
       </c>
       <c r="P60">
-        <v>-4.007578992139764</v>
+        <v>-4.168520009245622</v>
       </c>
       <c r="Q60">
-        <v>8.792421007860238</v>
+        <v>8.631479990754379</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1067382073965453</v>
+        <v>0.1082245051379244</v>
       </c>
       <c r="T60">
-        <v>1.407348900613055</v>
+        <v>1.441674483554837</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1712021507714155</v>
+        <v>0.1683004194024085</v>
       </c>
       <c r="W60">
-        <v>0.1664226081250998</v>
+        <v>0.1670052757839964</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5706738359047185</v>
+        <v>0.5610013980080284</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1429051598191069</v>
+        <v>0.1444551598191069</v>
       </c>
       <c r="C61">
-        <v>-24.9489009968975</v>
+        <v>-26.64527086121991</v>
       </c>
       <c r="D61">
-        <v>39.68602223336446</v>
+        <v>39.13465106786005</v>
       </c>
       <c r="E61">
-        <v>51.45505334846203</v>
+        <v>52.60005204728003</v>
       </c>
       <c r="F61">
-        <v>67.55492323026196</v>
+        <v>68.69992192907996</v>
       </c>
       <c r="G61">
         <v>2.92</v>
@@ -6289,37 +6289,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M61">
-        <v>13.5650285846366</v>
+        <v>13.79494432335926</v>
       </c>
       <c r="N61">
-        <v>-5.955028584636603</v>
+        <v>-6.184944323359257</v>
       </c>
       <c r="O61">
-        <v>-1.786508575390981</v>
+        <v>-1.855483297007777</v>
       </c>
       <c r="P61">
-        <v>-4.168520009245622</v>
+        <v>-4.32946102635148</v>
       </c>
       <c r="Q61">
-        <v>8.631479990754379</v>
+        <v>8.470538973648519</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1082245051379244</v>
+        <v>0.1097851177663726</v>
       </c>
       <c r="T61">
-        <v>1.441674483554837</v>
+        <v>1.477716345643708</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1683004194024085</v>
+        <v>0.1654954124123683</v>
       </c>
       <c r="W61">
-        <v>0.1670052757839964</v>
+        <v>0.1675685211875964</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5610013980080284</v>
+        <v>0.5516513747078945</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1444551598191069</v>
+        <v>0.1460051598191069</v>
       </c>
       <c r="C62">
-        <v>-26.64527086121991</v>
+        <v>-28.32652989770433</v>
       </c>
       <c r="D62">
-        <v>39.13465106786005</v>
+        <v>38.59839073019363</v>
       </c>
       <c r="E62">
-        <v>52.60005204728003</v>
+        <v>53.74505074609803</v>
       </c>
       <c r="F62">
-        <v>68.69992192907996</v>
+        <v>69.84492062789796</v>
       </c>
       <c r="G62">
         <v>2.92</v>
@@ -6371,37 +6371,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M62">
-        <v>13.79494432335926</v>
+        <v>14.02486006208191</v>
       </c>
       <c r="N62">
-        <v>-6.184944323359257</v>
+        <v>-6.414860062081912</v>
       </c>
       <c r="O62">
-        <v>-1.855483297007777</v>
+        <v>-1.924458018624573</v>
       </c>
       <c r="P62">
-        <v>-4.32946102635148</v>
+        <v>-4.490402043457339</v>
       </c>
       <c r="Q62">
-        <v>8.470538973648519</v>
+        <v>8.309597956542662</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1097851177663726</v>
+        <v>0.1114257618116642</v>
       </c>
       <c r="T62">
-        <v>1.477716345643708</v>
+        <v>1.515606508352521</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1654954124123683</v>
+        <v>0.1627823728646246</v>
       </c>
       <c r="W62">
-        <v>0.1675685211875964</v>
+        <v>0.1681132995287834</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5516513747078945</v>
+        <v>0.5426079095487486</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1460051598191069</v>
+        <v>0.1475551598191069</v>
       </c>
       <c r="C63">
-        <v>-28.32652989770433</v>
+        <v>-29.99329089824425</v>
       </c>
       <c r="D63">
-        <v>38.59839073019363</v>
+        <v>38.07662842847171</v>
       </c>
       <c r="E63">
-        <v>53.74505074609803</v>
+        <v>54.89004944491603</v>
       </c>
       <c r="F63">
-        <v>69.84492062789796</v>
+        <v>70.98991932671596</v>
       </c>
       <c r="G63">
         <v>2.92</v>
@@ -6453,37 +6453,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M63">
-        <v>14.02486006208191</v>
+        <v>14.25477580080457</v>
       </c>
       <c r="N63">
-        <v>-6.414860062081912</v>
+        <v>-6.644775800804567</v>
       </c>
       <c r="O63">
-        <v>-1.924458018624573</v>
+        <v>-1.99343274024137</v>
       </c>
       <c r="P63">
-        <v>-4.490402043457339</v>
+        <v>-4.651343060563197</v>
       </c>
       <c r="Q63">
-        <v>8.309597956542662</v>
+        <v>8.148656939436805</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1114257618116642</v>
+        <v>0.1131527555435501</v>
       </c>
       <c r="T63">
-        <v>1.515606508352521</v>
+        <v>1.555490890151272</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1627823728646246</v>
+        <v>0.1601568507216468</v>
       </c>
       <c r="W63">
-        <v>0.1681132995287834</v>
+        <v>0.1686405043750933</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5426079095487486</v>
+        <v>0.5338561690721559</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1475551598191069</v>
+        <v>0.1491051598191069</v>
       </c>
       <c r="C64">
-        <v>-29.99329089824425</v>
+        <v>-31.64613396245731</v>
       </c>
       <c r="D64">
-        <v>38.07662842847171</v>
+        <v>37.56878406307665</v>
       </c>
       <c r="E64">
-        <v>54.89004944491603</v>
+        <v>56.03504814373403</v>
       </c>
       <c r="F64">
-        <v>70.98991932671596</v>
+        <v>72.13491802553396</v>
       </c>
       <c r="G64">
         <v>2.92</v>
@@ -6535,37 +6535,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M64">
-        <v>14.25477580080457</v>
+        <v>14.48469153952722</v>
       </c>
       <c r="N64">
-        <v>-6.644775800804567</v>
+        <v>-6.874691539527221</v>
       </c>
       <c r="O64">
-        <v>-1.99343274024137</v>
+        <v>-2.062407461858166</v>
       </c>
       <c r="P64">
-        <v>-4.651343060563197</v>
+        <v>-4.812284077669055</v>
       </c>
       <c r="Q64">
-        <v>8.148656939436805</v>
+        <v>7.987715922330946</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1131527555435501</v>
+        <v>0.1149731002879703</v>
       </c>
       <c r="T64">
-        <v>1.555490890151272</v>
+        <v>1.597531184479685</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1601568507216468</v>
+        <v>0.1576146784879698</v>
       </c>
       <c r="W64">
-        <v>0.1686405043750933</v>
+        <v>0.1691509725596157</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5338561690721559</v>
+        <v>0.5253822616265662</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1491051598191069</v>
+        <v>0.1506551598191069</v>
       </c>
       <c r="C65">
-        <v>-31.64613396245731</v>
+        <v>-33.28560864914494</v>
       </c>
       <c r="D65">
-        <v>37.56878406307665</v>
+        <v>37.07430807520702</v>
       </c>
       <c r="E65">
-        <v>56.03504814373403</v>
+        <v>57.18004684255203</v>
       </c>
       <c r="F65">
-        <v>72.13491802553396</v>
+        <v>73.27991672435196</v>
       </c>
       <c r="G65">
         <v>2.92</v>
@@ -6617,37 +6617,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M65">
-        <v>14.48469153952722</v>
+        <v>14.71460727824988</v>
       </c>
       <c r="N65">
-        <v>-6.874691539527221</v>
+        <v>-7.104607278249876</v>
       </c>
       <c r="O65">
-        <v>-2.062407461858166</v>
+        <v>-2.131382183474963</v>
       </c>
       <c r="P65">
-        <v>-4.812284077669055</v>
+        <v>-4.973225094774913</v>
       </c>
       <c r="Q65">
-        <v>7.987715922330946</v>
+        <v>7.826774905225087</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1149731002879703</v>
+        <v>0.1168945752959695</v>
       </c>
       <c r="T65">
-        <v>1.597531184479685</v>
+        <v>1.641907050715231</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1576146784879698</v>
+        <v>0.1551519491365953</v>
       </c>
       <c r="W65">
-        <v>0.1691509725596157</v>
+        <v>0.1696454886133717</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5253822616265662</v>
+        <v>0.517173163788651</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1506551598191069</v>
+        <v>0.1522051598191069</v>
       </c>
       <c r="C66">
-        <v>-33.28560864914494</v>
+        <v>-34.91223596005592</v>
       </c>
       <c r="D66">
-        <v>37.07430807520702</v>
+        <v>36.59267946311404</v>
       </c>
       <c r="E66">
-        <v>57.18004684255203</v>
+        <v>58.32504554137003</v>
       </c>
       <c r="F66">
-        <v>73.27991672435196</v>
+        <v>74.42491542316996</v>
       </c>
       <c r="G66">
         <v>2.92</v>
@@ -6699,37 +6699,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M66">
-        <v>14.71460727824988</v>
+        <v>14.94452301697253</v>
       </c>
       <c r="N66">
-        <v>-7.104607278249876</v>
+        <v>-7.334523016972529</v>
       </c>
       <c r="O66">
-        <v>-2.131382183474963</v>
+        <v>-2.200356905091759</v>
       </c>
       <c r="P66">
-        <v>-4.973225094774913</v>
+        <v>-5.13416611188077</v>
       </c>
       <c r="Q66">
-        <v>7.826774905225087</v>
+        <v>7.665833888119231</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1168945752959695</v>
+        <v>0.1189258488758544</v>
       </c>
       <c r="T66">
-        <v>1.641907050715231</v>
+        <v>1.688818680735667</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1551519491365953</v>
+        <v>0.1527649960729554</v>
       </c>
       <c r="W66">
-        <v>0.1696454886133717</v>
+        <v>0.1701247887885506</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.517173163788651</v>
+        <v>0.5092166535765179</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1522051598191069</v>
+        <v>0.1537551598191069</v>
       </c>
       <c r="C67">
-        <v>-34.91223596005592</v>
+        <v>-36.52651017100733</v>
       </c>
       <c r="D67">
-        <v>36.59267946311404</v>
+        <v>36.12340395098063</v>
       </c>
       <c r="E67">
-        <v>58.32504554137003</v>
+        <v>59.47004424018803</v>
       </c>
       <c r="F67">
-        <v>74.42491542316996</v>
+        <v>75.56991412198796</v>
       </c>
       <c r="G67">
         <v>2.92</v>
@@ -6781,37 +6781,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M67">
-        <v>14.94452301697253</v>
+        <v>15.17443875569518</v>
       </c>
       <c r="N67">
-        <v>-7.334523016972529</v>
+        <v>-7.564438755695184</v>
       </c>
       <c r="O67">
-        <v>-2.200356905091759</v>
+        <v>-2.269331626708555</v>
       </c>
       <c r="P67">
-        <v>-5.13416611188077</v>
+        <v>-5.295107128986629</v>
       </c>
       <c r="Q67">
-        <v>7.665833888119231</v>
+        <v>7.504892871013372</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1189258488758544</v>
+        <v>0.1210766091369089</v>
       </c>
       <c r="T67">
-        <v>1.688818680735667</v>
+        <v>1.738489818404363</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1527649960729554</v>
+        <v>0.1504503749203349</v>
       </c>
       <c r="W67">
-        <v>0.1701247887885506</v>
+        <v>0.1705895647159968</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5092166535765179</v>
+        <v>0.5015012497344495</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1537551598191069</v>
+        <v>0.1791739716374834</v>
       </c>
       <c r="C68">
-        <v>-36.52651017100733</v>
+        <v>-43.94847438893844</v>
       </c>
       <c r="D68">
-        <v>36.12340395098063</v>
+        <v>29.84643843186752</v>
       </c>
       <c r="E68">
-        <v>59.47004424018803</v>
+        <v>60.61504293900603</v>
       </c>
       <c r="F68">
-        <v>75.56991412198796</v>
+        <v>76.71491282080596</v>
       </c>
       <c r="G68">
         <v>2.92</v>
@@ -6863,45 +6863,45 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M68">
-        <v>15.17443875569518</v>
+        <v>18.08937644314605</v>
       </c>
       <c r="N68">
-        <v>-7.564438755695184</v>
+        <v>-10.47937644314605</v>
       </c>
       <c r="O68">
-        <v>-2.269331626708555</v>
+        <v>-3.143812932943814</v>
       </c>
       <c r="P68">
-        <v>-5.295107128986629</v>
+        <v>-7.335563510202234</v>
       </c>
       <c r="Q68">
-        <v>7.504892871013372</v>
+        <v>5.464436489797767</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1210766091369089</v>
+        <v>0.1246268452270469</v>
       </c>
       <c r="T68">
-        <v>1.738489818404363</v>
+        <v>1.82048141401956</v>
       </c>
       <c r="U68">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1504503749203349</v>
+        <v>0.1262066720306998</v>
       </c>
       <c r="W68">
-        <v>0.1705895647159968</v>
+        <v>0.206040466735161</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.5015012497344495</v>
+        <v>0.4206889067689993</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1791739716374834</v>
+        <v>0.1810739716374833</v>
       </c>
       <c r="C69">
-        <v>-43.94847438893844</v>
+        <v>-45.47616336105115</v>
       </c>
       <c r="D69">
-        <v>29.84643843186752</v>
+        <v>29.46374815857282</v>
       </c>
       <c r="E69">
-        <v>60.61504293900603</v>
+        <v>61.76004163782403</v>
       </c>
       <c r="F69">
-        <v>76.71491282080596</v>
+        <v>77.85991151962396</v>
       </c>
       <c r="G69">
         <v>2.92</v>
@@ -6945,37 +6945,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M69">
-        <v>18.08937644314605</v>
+        <v>18.35936713632733</v>
       </c>
       <c r="N69">
-        <v>-10.47937644314605</v>
+        <v>-10.74936713632733</v>
       </c>
       <c r="O69">
-        <v>-3.143812932943814</v>
+        <v>-3.2248101408982</v>
       </c>
       <c r="P69">
-        <v>-7.335563510202234</v>
+        <v>-7.524556995429133</v>
       </c>
       <c r="Q69">
-        <v>5.464436489797767</v>
+        <v>5.275443004570867</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1246268452270469</v>
+        <v>0.1270901841403921</v>
       </c>
       <c r="T69">
-        <v>1.82048141401956</v>
+        <v>1.877371458207671</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1262066720306998</v>
+        <v>0.1243506915596601</v>
       </c>
       <c r="W69">
-        <v>0.206040466735161</v>
+        <v>0.2064781069302322</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4206889067689993</v>
+        <v>0.4145023051988669</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1810739716374833</v>
+        <v>0.1829739716374834</v>
       </c>
       <c r="C70">
-        <v>-45.47616336105115</v>
+        <v>-46.99416288119833</v>
       </c>
       <c r="D70">
-        <v>29.46374815857282</v>
+        <v>29.09074733724363</v>
       </c>
       <c r="E70">
-        <v>61.76004163782403</v>
+        <v>62.90504033664203</v>
       </c>
       <c r="F70">
-        <v>77.85991151962396</v>
+        <v>79.00491021844196</v>
       </c>
       <c r="G70">
         <v>2.92</v>
@@ -7027,37 +7027,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M70">
-        <v>18.35936713632733</v>
+        <v>18.62935782950862</v>
       </c>
       <c r="N70">
-        <v>-10.74936713632733</v>
+        <v>-11.01935782950862</v>
       </c>
       <c r="O70">
-        <v>-3.2248101408982</v>
+        <v>-3.305807348852585</v>
       </c>
       <c r="P70">
-        <v>-7.524556995429133</v>
+        <v>-7.713550480656032</v>
       </c>
       <c r="Q70">
-        <v>5.275443004570867</v>
+        <v>5.086449519343969</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1270901841403921</v>
+        <v>0.1297124481449209</v>
       </c>
       <c r="T70">
-        <v>1.877371458207671</v>
+        <v>1.937931827827273</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1243506915596601</v>
+        <v>0.1225485076240128</v>
       </c>
       <c r="W70">
-        <v>0.2064781069302322</v>
+        <v>0.2069030619022578</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4145023051988669</v>
+        <v>0.4084950254133761</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1829739716374834</v>
+        <v>0.1848739716374834</v>
       </c>
       <c r="C71">
-        <v>-46.99416288119833</v>
+        <v>-48.50283634422004</v>
       </c>
       <c r="D71">
-        <v>29.09074733724363</v>
+        <v>28.72707257303992</v>
       </c>
       <c r="E71">
-        <v>62.90504033664203</v>
+        <v>64.05003903546003</v>
       </c>
       <c r="F71">
-        <v>79.00491021844196</v>
+        <v>80.14990891725996</v>
       </c>
       <c r="G71">
         <v>2.92</v>
@@ -7109,37 +7109,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M71">
-        <v>18.62935782950862</v>
+        <v>18.8993485226899</v>
       </c>
       <c r="N71">
-        <v>-11.01935782950862</v>
+        <v>-11.2893485226899</v>
       </c>
       <c r="O71">
-        <v>-3.305807348852585</v>
+        <v>-3.38680455680697</v>
       </c>
       <c r="P71">
-        <v>-7.713550480656032</v>
+        <v>-7.902543965882932</v>
       </c>
       <c r="Q71">
-        <v>5.086449519343969</v>
+        <v>4.897456034117068</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1297124481449209</v>
+        <v>0.1325095297497516</v>
       </c>
       <c r="T71">
-        <v>1.937931827827273</v>
+        <v>2.002529555421516</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1225485076240128</v>
+        <v>0.1207978146579555</v>
       </c>
       <c r="W71">
-        <v>0.2069030619022578</v>
+        <v>0.2073158753036541</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4084950254133761</v>
+        <v>0.402659382193185</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1848739716374834</v>
+        <v>0.1867739716374834</v>
       </c>
       <c r="C72">
-        <v>-48.50283634422004</v>
+        <v>-50.00252919756196</v>
       </c>
       <c r="D72">
-        <v>28.72707257303992</v>
+        <v>28.37237841851601</v>
       </c>
       <c r="E72">
-        <v>64.05003903546003</v>
+        <v>65.19503773427803</v>
       </c>
       <c r="F72">
-        <v>80.14990891725996</v>
+        <v>81.29490761607796</v>
       </c>
       <c r="G72">
         <v>2.92</v>
@@ -7191,37 +7191,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M72">
-        <v>18.8993485226899</v>
+        <v>19.16933921587118</v>
       </c>
       <c r="N72">
-        <v>-11.2893485226899</v>
+        <v>-11.55933921587118</v>
       </c>
       <c r="O72">
-        <v>-3.38680455680697</v>
+        <v>-3.467801764761355</v>
       </c>
       <c r="P72">
-        <v>-7.902543965882932</v>
+        <v>-8.091537451109829</v>
       </c>
       <c r="Q72">
-        <v>4.897456034117068</v>
+        <v>4.708462548890171</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1325095297497516</v>
+        <v>0.1354995135342258</v>
       </c>
       <c r="T72">
-        <v>2.002529555421516</v>
+        <v>2.071582298711913</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1207978146579555</v>
+        <v>0.1190964369867167</v>
       </c>
       <c r="W72">
-        <v>0.2073158753036541</v>
+        <v>0.2077170601585322</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.402659382193185</v>
+        <v>0.3969881232890557</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1867739716374834</v>
+        <v>0.1886739716374833</v>
       </c>
       <c r="C73">
-        <v>-50.00252919756193</v>
+        <v>-51.49357003574726</v>
       </c>
       <c r="D73">
-        <v>28.37237841851602</v>
+        <v>28.02633627914869</v>
       </c>
       <c r="E73">
-        <v>65.19503773427802</v>
+        <v>66.34003643309602</v>
       </c>
       <c r="F73">
-        <v>81.29490761607795</v>
+        <v>82.43990631489595</v>
       </c>
       <c r="G73">
         <v>2.92</v>
@@ -7273,37 +7273,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M73">
-        <v>19.16933921587118</v>
+        <v>19.43932990905246</v>
       </c>
       <c r="N73">
-        <v>-11.55933921587118</v>
+        <v>-11.82932990905246</v>
       </c>
       <c r="O73">
-        <v>-3.467801764761355</v>
+        <v>-3.548798972715739</v>
       </c>
       <c r="P73">
-        <v>-8.091537451109829</v>
+        <v>-8.280530936336726</v>
       </c>
       <c r="Q73">
-        <v>4.708462548890171</v>
+        <v>4.519469063663275</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1354995135342258</v>
+        <v>0.1387030675890195</v>
       </c>
       <c r="T73">
-        <v>2.071582298711912</v>
+        <v>2.145567380808766</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1190964369867167</v>
+        <v>0.1174423198063456</v>
       </c>
       <c r="W73">
-        <v>0.2077170601585322</v>
+        <v>0.2081071009896637</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3969881232890557</v>
+        <v>0.3914743993544856</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1886739716374833</v>
+        <v>0.1905739716374834</v>
       </c>
       <c r="C74">
-        <v>-51.49357003574726</v>
+        <v>-52.9762716157219</v>
       </c>
       <c r="D74">
-        <v>28.02633627914869</v>
+        <v>27.68863339799205</v>
       </c>
       <c r="E74">
-        <v>66.34003643309602</v>
+        <v>67.48503513191402</v>
       </c>
       <c r="F74">
-        <v>82.43990631489595</v>
+        <v>83.58490501371395</v>
       </c>
       <c r="G74">
         <v>2.92</v>
@@ -7355,37 +7355,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M74">
-        <v>19.43932990905246</v>
+        <v>19.70932060223375</v>
       </c>
       <c r="N74">
-        <v>-11.82932990905246</v>
+        <v>-12.09932060223375</v>
       </c>
       <c r="O74">
-        <v>-3.548798972715739</v>
+        <v>-3.629796180670125</v>
       </c>
       <c r="P74">
-        <v>-8.280530936336726</v>
+        <v>-8.469524421563625</v>
       </c>
       <c r="Q74">
-        <v>4.519469063663275</v>
+        <v>4.330475578436376</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1387030675890195</v>
+        <v>0.1421439219441684</v>
       </c>
       <c r="T74">
-        <v>2.145567380808766</v>
+        <v>2.225032839357239</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1174423198063456</v>
+        <v>0.1158335209048889</v>
       </c>
       <c r="W74">
-        <v>0.2081071009896637</v>
+        <v>0.2084864557706272</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3914743993544856</v>
+        <v>0.3861117363496296</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1905739716374834</v>
+        <v>0.1924739716374833</v>
       </c>
       <c r="C75">
-        <v>-52.9762716157219</v>
+        <v>-54.45093179966707</v>
       </c>
       <c r="D75">
-        <v>27.68863339799205</v>
+        <v>27.35897191286488</v>
       </c>
       <c r="E75">
-        <v>67.48503513191402</v>
+        <v>68.63003383073202</v>
       </c>
       <c r="F75">
-        <v>83.58490501371395</v>
+        <v>84.72990371253195</v>
       </c>
       <c r="G75">
         <v>2.92</v>
@@ -7437,37 +7437,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M75">
-        <v>19.70932060223375</v>
+        <v>19.97931129541503</v>
       </c>
       <c r="N75">
-        <v>-12.09932060223375</v>
+        <v>-12.36931129541503</v>
       </c>
       <c r="O75">
-        <v>-3.629796180670125</v>
+        <v>-3.71079338862451</v>
       </c>
       <c r="P75">
-        <v>-8.469524421563625</v>
+        <v>-8.658517906790525</v>
       </c>
       <c r="Q75">
-        <v>4.330475578436376</v>
+        <v>4.141482093209476</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1421439219441684</v>
+        <v>0.1458494574035595</v>
       </c>
       <c r="T75">
-        <v>2.225032839357239</v>
+        <v>2.310611025486363</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1158335209048889</v>
+        <v>0.1142682030548228</v>
       </c>
       <c r="W75">
-        <v>0.2084864557706272</v>
+        <v>0.2088555577196728</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3861117363496296</v>
+        <v>0.3808940101827427</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1924739716374833</v>
+        <v>0.1943739716374834</v>
       </c>
       <c r="C76">
-        <v>-54.45093179966707</v>
+        <v>-55.91783443125372</v>
       </c>
       <c r="D76">
-        <v>27.35897191286488</v>
+        <v>27.03706798009624</v>
       </c>
       <c r="E76">
-        <v>68.63003383073202</v>
+        <v>69.77503252955002</v>
       </c>
       <c r="F76">
-        <v>84.72990371253195</v>
+        <v>85.87490241134995</v>
       </c>
       <c r="G76">
         <v>2.92</v>
@@ -7519,37 +7519,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M76">
-        <v>19.97931129541503</v>
+        <v>20.24930198859632</v>
       </c>
       <c r="N76">
-        <v>-12.36931129541503</v>
+        <v>-12.63930198859632</v>
       </c>
       <c r="O76">
-        <v>-3.71079338862451</v>
+        <v>-3.791790596578895</v>
       </c>
       <c r="P76">
-        <v>-8.658517906790525</v>
+        <v>-8.847511392017424</v>
       </c>
       <c r="Q76">
-        <v>4.141482093209476</v>
+        <v>3.952488607982577</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1458494574035595</v>
+        <v>0.1498514356997019</v>
       </c>
       <c r="T76">
-        <v>2.310611025486363</v>
+        <v>2.403035466505818</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1142682030548228</v>
+        <v>0.1127446270140918</v>
       </c>
       <c r="W76">
-        <v>0.2088555577196728</v>
+        <v>0.2092148169500772</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3808940101827427</v>
+        <v>0.375815423380306</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1943739716374834</v>
+        <v>0.1962739716374833</v>
       </c>
       <c r="C77">
-        <v>-55.91783443125372</v>
+        <v>-57.37725015075637</v>
       </c>
       <c r="D77">
-        <v>27.03706798009624</v>
+        <v>26.72265095941158</v>
       </c>
       <c r="E77">
-        <v>69.77503252955002</v>
+        <v>70.92003122836802</v>
       </c>
       <c r="F77">
-        <v>85.87490241134995</v>
+        <v>87.01990111016795</v>
       </c>
       <c r="G77">
         <v>2.92</v>
@@ -7601,37 +7601,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M77">
-        <v>20.24930198859632</v>
+        <v>20.5192926817776</v>
       </c>
       <c r="N77">
-        <v>-12.63930198859632</v>
+        <v>-12.9092926817776</v>
       </c>
       <c r="O77">
-        <v>-3.791790596578895</v>
+        <v>-3.872787804533281</v>
       </c>
       <c r="P77">
-        <v>-8.847511392017424</v>
+        <v>-9.036504877244322</v>
       </c>
       <c r="Q77">
-        <v>3.952488607982577</v>
+        <v>3.763495122755678</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1498514356997019</v>
+        <v>0.1541869121871895</v>
       </c>
       <c r="T77">
-        <v>2.403035466505818</v>
+        <v>2.503161944276894</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1127446270140918</v>
+        <v>0.1112611450796959</v>
       </c>
       <c r="W77">
-        <v>0.2092148169500772</v>
+        <v>0.2095646219902077</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.375815423380306</v>
+        <v>0.3708704835989862</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1962739716374833</v>
+        <v>0.1981739716374833</v>
       </c>
       <c r="C78">
-        <v>-57.37725015075637</v>
+        <v>-58.82943715394669</v>
       </c>
       <c r="D78">
-        <v>26.72265095941158</v>
+        <v>26.41546265503926</v>
       </c>
       <c r="E78">
-        <v>70.92003122836802</v>
+        <v>72.06502992718602</v>
       </c>
       <c r="F78">
-        <v>87.01990111016795</v>
+        <v>88.16489980898595</v>
       </c>
       <c r="G78">
         <v>2.92</v>
@@ -7683,37 +7683,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M78">
-        <v>20.5192926817776</v>
+        <v>20.78928337495889</v>
       </c>
       <c r="N78">
-        <v>-12.9092926817776</v>
+        <v>-13.17928337495889</v>
       </c>
       <c r="O78">
-        <v>-3.872787804533281</v>
+        <v>-3.953785012487666</v>
       </c>
       <c r="P78">
-        <v>-9.036504877244322</v>
+        <v>-9.225498362471223</v>
       </c>
       <c r="Q78">
-        <v>3.763495122755678</v>
+        <v>3.574501637528778</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1541869121871895</v>
+        <v>0.1588993866301108</v>
       </c>
       <c r="T78">
-        <v>2.503161944276894</v>
+        <v>2.611995072288933</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1112611450796959</v>
+        <v>0.1098161951435959</v>
       </c>
       <c r="W78">
-        <v>0.2095646219902077</v>
+        <v>0.2099053411851401</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3708704835989862</v>
+        <v>0.3660539838119864</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1981739716374833</v>
+        <v>0.2000739716374833</v>
       </c>
       <c r="C79">
-        <v>-58.82943715394669</v>
+        <v>-60.27464189923879</v>
       </c>
       <c r="D79">
-        <v>26.41546265503926</v>
+        <v>26.11525660856516</v>
       </c>
       <c r="E79">
-        <v>72.06502992718602</v>
+        <v>73.21002862600402</v>
       </c>
       <c r="F79">
-        <v>88.16489980898595</v>
+        <v>89.30989850780395</v>
       </c>
       <c r="G79">
         <v>2.92</v>
@@ -7765,37 +7765,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M79">
-        <v>20.78928337495889</v>
+        <v>21.05927406814017</v>
       </c>
       <c r="N79">
-        <v>-13.17928337495889</v>
+        <v>-13.44927406814017</v>
       </c>
       <c r="O79">
-        <v>-3.953785012487666</v>
+        <v>-4.034782220442052</v>
       </c>
       <c r="P79">
-        <v>-9.225498362471223</v>
+        <v>-9.414491847698121</v>
       </c>
       <c r="Q79">
-        <v>3.574501637528778</v>
+        <v>3.385508152301879</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1588993866301108</v>
+        <v>0.1640402678405704</v>
       </c>
       <c r="T79">
-        <v>2.611995072288933</v>
+        <v>2.73072212102934</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1098161951435959</v>
+        <v>0.1084082952058575</v>
       </c>
       <c r="W79">
-        <v>0.2099053411851401</v>
+        <v>0.2102373239904588</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3660539838119864</v>
+        <v>0.3613609840195251</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2000739716374833</v>
+        <v>0.2019739716374834</v>
       </c>
       <c r="C80">
-        <v>-60.27464189923879</v>
+        <v>-61.71309976715746</v>
       </c>
       <c r="D80">
-        <v>26.11525660856516</v>
+        <v>25.82179743946449</v>
       </c>
       <c r="E80">
-        <v>73.21002862600402</v>
+        <v>74.35502732482202</v>
       </c>
       <c r="F80">
-        <v>89.30989850780395</v>
+        <v>90.45489720662195</v>
       </c>
       <c r="G80">
         <v>2.92</v>
@@ -7847,37 +7847,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M80">
-        <v>21.05927406814017</v>
+        <v>21.32926476132146</v>
       </c>
       <c r="N80">
-        <v>-13.44927406814017</v>
+        <v>-13.71926476132146</v>
       </c>
       <c r="O80">
-        <v>-4.034782220442052</v>
+        <v>-4.115779428396437</v>
       </c>
       <c r="P80">
-        <v>-9.414491847698121</v>
+        <v>-9.603485332925022</v>
       </c>
       <c r="Q80">
-        <v>3.385508152301879</v>
+        <v>3.196514667074979</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1640402678405704</v>
+        <v>0.1696707567853595</v>
       </c>
       <c r="T80">
-        <v>2.73072212102934</v>
+        <v>2.860756507745022</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1084082952058575</v>
+        <v>0.1070360383045176</v>
       </c>
       <c r="W80">
-        <v>0.2102373239904588</v>
+        <v>0.2105609021677948</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3613609840195251</v>
+        <v>0.3567867943483918</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2019739716374834</v>
+        <v>0.2038739716374833</v>
       </c>
       <c r="C81">
-        <v>-61.71309976715746</v>
+        <v>-63.14503567583702</v>
       </c>
       <c r="D81">
-        <v>25.82179743946449</v>
+        <v>25.53486022960293</v>
       </c>
       <c r="E81">
-        <v>74.35502732482202</v>
+        <v>75.50002602364002</v>
       </c>
       <c r="F81">
-        <v>90.45489720662195</v>
+        <v>91.59989590543995</v>
       </c>
       <c r="G81">
         <v>2.92</v>
@@ -7929,37 +7929,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M81">
-        <v>21.32926476132146</v>
+        <v>21.59925545450274</v>
       </c>
       <c r="N81">
-        <v>-13.71926476132146</v>
+        <v>-13.98925545450274</v>
       </c>
       <c r="O81">
-        <v>-4.115779428396437</v>
+        <v>-4.196776636350823</v>
       </c>
       <c r="P81">
-        <v>-9.603485332925022</v>
+        <v>-9.79247881815192</v>
       </c>
       <c r="Q81">
-        <v>3.196514667074979</v>
+        <v>3.00752118184808</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1696707567853595</v>
+        <v>0.1758642946246274</v>
       </c>
       <c r="T81">
-        <v>2.860756507745022</v>
+        <v>3.003794333132273</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1070360383045176</v>
+        <v>0.1056980878257111</v>
       </c>
       <c r="W81">
-        <v>0.2105609021677948</v>
+        <v>0.2108763908906973</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3567867943483918</v>
+        <v>0.3523269594190369</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2038739716374833</v>
+        <v>0.2057739716374834</v>
       </c>
       <c r="C82">
-        <v>-63.14503567583702</v>
+        <v>-64.57066465593434</v>
       </c>
       <c r="D82">
-        <v>25.53486022960293</v>
+        <v>25.25422994832361</v>
       </c>
       <c r="E82">
-        <v>75.50002602364002</v>
+        <v>76.64502472245802</v>
       </c>
       <c r="F82">
-        <v>91.59989590543995</v>
+        <v>92.74489460425795</v>
       </c>
       <c r="G82">
         <v>2.92</v>
@@ -8011,37 +8011,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M82">
-        <v>21.59925545450274</v>
+        <v>21.86924614768403</v>
       </c>
       <c r="N82">
-        <v>-13.98925545450274</v>
+        <v>-14.25924614768403</v>
       </c>
       <c r="O82">
-        <v>-4.196776636350823</v>
+        <v>-4.277773844305208</v>
       </c>
       <c r="P82">
-        <v>-9.79247881815192</v>
+        <v>-9.981472303378819</v>
       </c>
       <c r="Q82">
-        <v>3.00752118184808</v>
+        <v>2.818527696621182</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1758642946246274</v>
+        <v>0.1827097838153973</v>
       </c>
       <c r="T82">
-        <v>3.003794333132273</v>
+        <v>3.161888771718183</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1056980878257111</v>
+        <v>0.1043931731611961</v>
       </c>
       <c r="W82">
-        <v>0.2108763908906973</v>
+        <v>0.21118408976859</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3523269594190369</v>
+        <v>0.3479772438706538</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2057739716374834</v>
+        <v>0.2076739716374834</v>
       </c>
       <c r="C83">
-        <v>-64.57066465593434</v>
+        <v>-65.99019238804354</v>
       </c>
       <c r="D83">
-        <v>25.25422994832361</v>
+        <v>24.97970091503241</v>
       </c>
       <c r="E83">
-        <v>76.64502472245802</v>
+        <v>77.79002342127602</v>
       </c>
       <c r="F83">
-        <v>92.74489460425795</v>
+        <v>93.88989330307595</v>
       </c>
       <c r="G83">
         <v>2.92</v>
@@ -8093,37 +8093,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M83">
-        <v>21.86924614768403</v>
+        <v>22.13923684086531</v>
       </c>
       <c r="N83">
-        <v>-14.25924614768403</v>
+        <v>-14.52923684086531</v>
       </c>
       <c r="O83">
-        <v>-4.277773844305208</v>
+        <v>-4.358771052259592</v>
       </c>
       <c r="P83">
-        <v>-9.981472303378819</v>
+        <v>-10.17046578860572</v>
       </c>
       <c r="Q83">
-        <v>2.818527696621182</v>
+        <v>2.629534211394283</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1827097838153973</v>
+        <v>0.1903158829162527</v>
       </c>
       <c r="T83">
-        <v>3.161888771718183</v>
+        <v>3.33754925903586</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1043931731611961</v>
+        <v>0.1031200856836206</v>
       </c>
       <c r="W83">
-        <v>0.21118408976859</v>
+        <v>0.2114842837958023</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3479772438706538</v>
+        <v>0.3437336189454019</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2076739716374834</v>
+        <v>0.2095739716374834</v>
       </c>
       <c r="C84">
-        <v>-65.99019238804354</v>
+        <v>-67.40381570543565</v>
       </c>
       <c r="D84">
-        <v>24.97970091503241</v>
+        <v>24.7110762964583</v>
       </c>
       <c r="E84">
-        <v>77.79002342127602</v>
+        <v>78.93502212009402</v>
       </c>
       <c r="F84">
-        <v>93.88989330307595</v>
+        <v>95.03489200189395</v>
       </c>
       <c r="G84">
         <v>2.92</v>
@@ -8175,37 +8175,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M84">
-        <v>22.13923684086531</v>
+        <v>22.40922753404659</v>
       </c>
       <c r="N84">
-        <v>-14.52923684086531</v>
+        <v>-14.79922753404659</v>
       </c>
       <c r="O84">
-        <v>-4.358771052259592</v>
+        <v>-4.439768260213978</v>
       </c>
       <c r="P84">
-        <v>-10.17046578860572</v>
+        <v>-10.35945927383262</v>
       </c>
       <c r="Q84">
-        <v>2.629534211394283</v>
+        <v>2.440540726167384</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1903158829162527</v>
+        <v>0.1988168172054441</v>
       </c>
       <c r="T84">
-        <v>3.33754925903586</v>
+        <v>3.53387568603797</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1031200856836206</v>
+        <v>0.1018776750127336</v>
       </c>
       <c r="W84">
-        <v>0.2114842837958023</v>
+        <v>0.2117772442319974</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3437336189454019</v>
+        <v>0.3395922500424452</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2095739716374834</v>
+        <v>0.2114739716374834</v>
       </c>
       <c r="C85">
-        <v>-67.40381570543565</v>
+        <v>-68.81172306470549</v>
       </c>
       <c r="D85">
-        <v>24.7110762964583</v>
+        <v>24.44816763600646</v>
       </c>
       <c r="E85">
-        <v>78.93502212009402</v>
+        <v>80.08002081891202</v>
       </c>
       <c r="F85">
-        <v>95.03489200189395</v>
+        <v>96.17989070071195</v>
       </c>
       <c r="G85">
         <v>2.92</v>
@@ -8257,37 +8257,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M85">
-        <v>22.40922753404659</v>
+        <v>22.67921822722788</v>
       </c>
       <c r="N85">
-        <v>-14.79922753404659</v>
+        <v>-15.06921822722788</v>
       </c>
       <c r="O85">
-        <v>-4.439768260213978</v>
+        <v>-4.520765468168364</v>
       </c>
       <c r="P85">
-        <v>-10.35945927383262</v>
+        <v>-10.54845275905951</v>
       </c>
       <c r="Q85">
-        <v>2.440540726167384</v>
+        <v>2.251547240940486</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1988168172054441</v>
+        <v>0.2083803682807844</v>
       </c>
       <c r="T85">
-        <v>3.53387568603797</v>
+        <v>3.754742916415343</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1018776750127336</v>
+        <v>0.1006648455482963</v>
       </c>
       <c r="W85">
-        <v>0.2117772442319974</v>
+        <v>0.2120632294197118</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3395922500424452</v>
+        <v>0.3355494851609876</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2114739716374833</v>
+        <v>0.2133739716374833</v>
       </c>
       <c r="C86">
-        <v>-68.81172306470548</v>
+        <v>-70.2140949866905</v>
       </c>
       <c r="D86">
-        <v>24.44816763600647</v>
+        <v>24.19079441283946</v>
       </c>
       <c r="E86">
-        <v>80.08002081891202</v>
+        <v>81.22501951773002</v>
       </c>
       <c r="F86">
-        <v>96.17989070071195</v>
+        <v>97.32488939952995</v>
       </c>
       <c r="G86">
         <v>2.92</v>
@@ -8339,37 +8339,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M86">
-        <v>22.67921822722788</v>
+        <v>22.94920892040916</v>
       </c>
       <c r="N86">
-        <v>-15.06921822722788</v>
+        <v>-15.33920892040916</v>
       </c>
       <c r="O86">
-        <v>-4.520765468168364</v>
+        <v>-4.601762676122749</v>
       </c>
       <c r="P86">
-        <v>-10.54845275905951</v>
+        <v>-10.73744624428641</v>
       </c>
       <c r="Q86">
-        <v>2.251547240940486</v>
+        <v>2.062553755713587</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2083803682807842</v>
+        <v>0.2192190594995032</v>
       </c>
       <c r="T86">
-        <v>3.754742916415341</v>
+        <v>4.00505911084303</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1006648455482963</v>
+        <v>0.09948055324772807</v>
       </c>
       <c r="W86">
-        <v>0.2120632294197118</v>
+        <v>0.2123424855441857</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3355494851609876</v>
+        <v>0.3316018441590936</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2133739716374833</v>
+        <v>0.2152739716374834</v>
       </c>
       <c r="C87">
-        <v>-70.2140949866905</v>
+        <v>-71.61110446982981</v>
       </c>
       <c r="D87">
-        <v>24.19079441283946</v>
+        <v>23.93878362851814</v>
       </c>
       <c r="E87">
-        <v>81.22501951773002</v>
+        <v>82.37001821654802</v>
       </c>
       <c r="F87">
-        <v>97.32488939952995</v>
+        <v>98.46988809834795</v>
       </c>
       <c r="G87">
         <v>2.92</v>
@@ -8421,37 +8421,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M87">
-        <v>22.94920892040916</v>
+        <v>23.21919961359045</v>
       </c>
       <c r="N87">
-        <v>-15.33920892040916</v>
+        <v>-15.60919961359045</v>
       </c>
       <c r="O87">
-        <v>-4.601762676122749</v>
+        <v>-4.682759884077134</v>
       </c>
       <c r="P87">
-        <v>-10.73744624428641</v>
+        <v>-10.92643972951331</v>
       </c>
       <c r="Q87">
-        <v>2.062553755713587</v>
+        <v>1.873560270486687</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2192190594995032</v>
+        <v>0.2316061351780392</v>
       </c>
       <c r="T87">
-        <v>4.00505911084303</v>
+        <v>4.291134761617533</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09948055324772807</v>
+        <v>0.09832380262856844</v>
       </c>
       <c r="W87">
-        <v>0.2123424855441857</v>
+        <v>0.2126152473401836</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3316018441590936</v>
+        <v>0.3277460087618949</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2152739716374834</v>
+        <v>0.2171739716374834</v>
       </c>
       <c r="C88">
-        <v>-71.61110446982981</v>
+        <v>-73.00291737795233</v>
       </c>
       <c r="D88">
-        <v>23.93878362851814</v>
+        <v>23.69196941921362</v>
       </c>
       <c r="E88">
-        <v>82.37001821654802</v>
+        <v>83.51501691536602</v>
       </c>
       <c r="F88">
-        <v>98.46988809834795</v>
+        <v>99.61488679716595</v>
       </c>
       <c r="G88">
         <v>2.92</v>
@@ -8503,37 +8503,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M88">
-        <v>23.21919961359045</v>
+        <v>23.48919030677173</v>
       </c>
       <c r="N88">
-        <v>-15.60919961359045</v>
+        <v>-15.87919030677173</v>
       </c>
       <c r="O88">
-        <v>-4.682759884077134</v>
+        <v>-4.763757092031519</v>
       </c>
       <c r="P88">
-        <v>-10.92643972951331</v>
+        <v>-11.11543321474021</v>
       </c>
       <c r="Q88">
-        <v>1.873560270486687</v>
+        <v>1.684566785259786</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2316061351780392</v>
+        <v>0.245898914807119</v>
       </c>
       <c r="T88">
-        <v>4.291134761617533</v>
+        <v>4.621222050972727</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09832380262856844</v>
+        <v>0.09719364397766535</v>
       </c>
       <c r="W88">
-        <v>0.2126152473401836</v>
+        <v>0.2128817387500665</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3277460087618949</v>
+        <v>0.3239788132588846</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2171739716374834</v>
+        <v>0.2190739716374834</v>
       </c>
       <c r="C89">
-        <v>-73.00291737795233</v>
+        <v>-74.38969280432035</v>
       </c>
       <c r="D89">
-        <v>23.69196941921362</v>
+        <v>23.4501926916636</v>
       </c>
       <c r="E89">
-        <v>83.51501691536602</v>
+        <v>84.66001561418402</v>
       </c>
       <c r="F89">
-        <v>99.61488679716595</v>
+        <v>100.759885495984</v>
       </c>
       <c r="G89">
         <v>2.92</v>
@@ -8585,37 +8585,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M89">
-        <v>23.48919030677173</v>
+        <v>23.75918099995302</v>
       </c>
       <c r="N89">
-        <v>-15.87919030677173</v>
+        <v>-16.14918099995302</v>
       </c>
       <c r="O89">
-        <v>-4.763757092031519</v>
+        <v>-4.844754299985905</v>
       </c>
       <c r="P89">
-        <v>-11.11543321474021</v>
+        <v>-11.30442669996711</v>
       </c>
       <c r="Q89">
-        <v>1.684566785259786</v>
+        <v>1.495573300032888</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.245898914807119</v>
+        <v>0.262573824374379</v>
       </c>
       <c r="T89">
-        <v>4.621222050972727</v>
+        <v>5.006323888553789</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09719364397766535</v>
+        <v>0.09608917075064642</v>
       </c>
       <c r="W89">
-        <v>0.2128817387500665</v>
+        <v>0.2131421735369976</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3239788132588846</v>
+        <v>0.3202972358354881</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2190739716374834</v>
+        <v>0.2209739716374834</v>
       </c>
       <c r="C90">
-        <v>-74.38969280432035</v>
+        <v>-75.77158341360824</v>
       </c>
       <c r="D90">
-        <v>23.4501926916636</v>
+        <v>23.21330078119371</v>
       </c>
       <c r="E90">
-        <v>84.66001561418402</v>
+        <v>85.80501431300202</v>
       </c>
       <c r="F90">
-        <v>100.759885495984</v>
+        <v>101.904884194802</v>
       </c>
       <c r="G90">
         <v>2.92</v>
@@ -8667,37 +8667,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M90">
-        <v>23.75918099995302</v>
+        <v>24.0291716931343</v>
       </c>
       <c r="N90">
-        <v>-16.14918099995302</v>
+        <v>-16.4191716931343</v>
       </c>
       <c r="O90">
-        <v>-4.844754299985905</v>
+        <v>-4.925751507940291</v>
       </c>
       <c r="P90">
-        <v>-11.30442669996711</v>
+        <v>-11.49342018519401</v>
       </c>
       <c r="Q90">
-        <v>1.495573300032888</v>
+        <v>1.306579814805989</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.262573824374379</v>
+        <v>0.2822805356811408</v>
       </c>
       <c r="T90">
-        <v>5.006323888553789</v>
+        <v>5.461444242058679</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09608917075064642</v>
+        <v>0.09500951714670658</v>
       </c>
       <c r="W90">
-        <v>0.2131421735369976</v>
+        <v>0.2133967558568066</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3202972358354881</v>
+        <v>0.3166983904890219</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2209739716374834</v>
+        <v>0.2228739716374833</v>
       </c>
       <c r="C91">
-        <v>-75.77158341360824</v>
+        <v>-77.14873576336028</v>
       </c>
       <c r="D91">
-        <v>23.21330078119371</v>
+        <v>22.98114713025967</v>
       </c>
       <c r="E91">
-        <v>85.80501431300202</v>
+        <v>86.95001301182002</v>
       </c>
       <c r="F91">
-        <v>101.904884194802</v>
+        <v>103.04988289362</v>
       </c>
       <c r="G91">
         <v>2.92</v>
@@ -8749,37 +8749,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M91">
-        <v>24.0291716931343</v>
+        <v>24.29916238631559</v>
       </c>
       <c r="N91">
-        <v>-16.4191716931343</v>
+        <v>-16.68916238631559</v>
       </c>
       <c r="O91">
-        <v>-4.925751507940291</v>
+        <v>-5.006748715894676</v>
       </c>
       <c r="P91">
-        <v>-11.49342018519401</v>
+        <v>-11.68241367042091</v>
       </c>
       <c r="Q91">
-        <v>1.306579814805989</v>
+        <v>1.11758632957909</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2822805356811408</v>
+        <v>0.3059285892492548</v>
       </c>
       <c r="T91">
-        <v>5.461444242058679</v>
+        <v>6.007588666264547</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09500951714670658</v>
+        <v>0.0939538558450765</v>
       </c>
       <c r="W91">
-        <v>0.2133967558568066</v>
+        <v>0.213645680791731</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3166983904890219</v>
+        <v>0.3131795194835884</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2228739716374833</v>
+        <v>0.2247739716374834</v>
       </c>
       <c r="C92">
-        <v>-77.14873576336028</v>
+        <v>-78.52129060635058</v>
       </c>
       <c r="D92">
-        <v>22.98114713025967</v>
+        <v>22.75359098608737</v>
       </c>
       <c r="E92">
-        <v>86.95001301182002</v>
+        <v>88.09501171063802</v>
       </c>
       <c r="F92">
-        <v>103.04988289362</v>
+        <v>104.194881592438</v>
       </c>
       <c r="G92">
         <v>2.92</v>
@@ -8831,37 +8831,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M92">
-        <v>24.29916238631559</v>
+        <v>24.56915307949687</v>
       </c>
       <c r="N92">
-        <v>-16.68916238631559</v>
+        <v>-16.95915307949687</v>
       </c>
       <c r="O92">
-        <v>-5.006748715894676</v>
+        <v>-5.087745923849061</v>
       </c>
       <c r="P92">
-        <v>-11.68241367042091</v>
+        <v>-11.87140715564781</v>
       </c>
       <c r="Q92">
-        <v>1.11758632957909</v>
+        <v>0.92859284435219</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3059285892492548</v>
+        <v>0.3348317658325054</v>
       </c>
       <c r="T92">
-        <v>6.007588666264547</v>
+        <v>6.67509851807172</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0939538558450765</v>
+        <v>0.092921395890735</v>
       </c>
       <c r="W92">
-        <v>0.213645680791731</v>
+        <v>0.2138891348489647</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3131795194835884</v>
+        <v>0.30973798630245</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2247739716374834</v>
+        <v>0.2266739716374833</v>
       </c>
       <c r="C93">
-        <v>-78.52129060635058</v>
+        <v>-79.88938317515536</v>
       </c>
       <c r="D93">
-        <v>22.75359098608737</v>
+        <v>22.5304971161006</v>
       </c>
       <c r="E93">
-        <v>88.09501171063802</v>
+        <v>89.24001040945602</v>
       </c>
       <c r="F93">
-        <v>104.194881592438</v>
+        <v>105.339880291256</v>
       </c>
       <c r="G93">
         <v>2.92</v>
@@ -8913,37 +8913,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M93">
-        <v>24.56915307949687</v>
+        <v>24.83914377267816</v>
       </c>
       <c r="N93">
-        <v>-16.95915307949687</v>
+        <v>-17.22914377267816</v>
       </c>
       <c r="O93">
-        <v>-5.087745923849061</v>
+        <v>-5.168743131803446</v>
       </c>
       <c r="P93">
-        <v>-11.87140715564781</v>
+        <v>-12.06040064087471</v>
       </c>
       <c r="Q93">
-        <v>0.92859284435219</v>
+        <v>0.7395993591252896</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3348317658325054</v>
+        <v>0.3709607365615687</v>
       </c>
       <c r="T93">
-        <v>6.67509851807172</v>
+        <v>7.509485832830687</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.092921395890735</v>
+        <v>0.09191138071800962</v>
       </c>
       <c r="W93">
-        <v>0.2138891348489647</v>
+        <v>0.2141272964266933</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.30973798630245</v>
+        <v>0.3063712690600321</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2266739716374833</v>
+        <v>0.2285739716374834</v>
       </c>
       <c r="C94">
-        <v>-79.88938317515536</v>
+        <v>-81.25314345014685</v>
       </c>
       <c r="D94">
-        <v>22.5304971161006</v>
+        <v>22.3117355399271</v>
       </c>
       <c r="E94">
-        <v>89.24001040945602</v>
+        <v>90.38500910827402</v>
       </c>
       <c r="F94">
-        <v>105.339880291256</v>
+        <v>106.484878990074</v>
       </c>
       <c r="G94">
         <v>2.92</v>
@@ -8995,37 +8995,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M94">
-        <v>24.83914377267816</v>
+        <v>25.10913446585944</v>
       </c>
       <c r="N94">
-        <v>-17.22914377267816</v>
+        <v>-17.49913446585944</v>
       </c>
       <c r="O94">
-        <v>-5.168743131803446</v>
+        <v>-5.249740339757831</v>
       </c>
       <c r="P94">
-        <v>-12.06040064087471</v>
+        <v>-12.24939412610161</v>
       </c>
       <c r="Q94">
-        <v>0.7395993591252896</v>
+        <v>0.5506058738983945</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3709607365615687</v>
+        <v>0.4174122703560785</v>
       </c>
       <c r="T94">
-        <v>7.509485832830687</v>
+        <v>8.582269523235071</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09191138071800962</v>
+        <v>0.09092308630168694</v>
       </c>
       <c r="W94">
-        <v>0.2141272964266933</v>
+        <v>0.2143603362500622</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3063712690600321</v>
+        <v>0.3030769543389565</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2285739716374834</v>
+        <v>0.2304739716374834</v>
       </c>
       <c r="C95">
-        <v>-81.25314345014685</v>
+        <v>-82.61269641202479</v>
       </c>
       <c r="D95">
-        <v>22.3117355399271</v>
+        <v>22.09718127686716</v>
       </c>
       <c r="E95">
-        <v>90.38500910827402</v>
+        <v>91.53000780709202</v>
       </c>
       <c r="F95">
-        <v>106.484878990074</v>
+        <v>107.629877688892</v>
       </c>
       <c r="G95">
         <v>2.92</v>
@@ -9077,37 +9077,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M95">
-        <v>25.10913446585944</v>
+        <v>25.37912515904072</v>
       </c>
       <c r="N95">
-        <v>-17.49913446585944</v>
+        <v>-17.76912515904072</v>
       </c>
       <c r="O95">
-        <v>-5.249740339757831</v>
+        <v>-5.330737547712217</v>
       </c>
       <c r="P95">
-        <v>-12.24939412610161</v>
+        <v>-12.4383876113285</v>
       </c>
       <c r="Q95">
-        <v>0.5506058738983945</v>
+        <v>0.3616123886714959</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4174122703560785</v>
+        <v>0.4793476487487584</v>
       </c>
       <c r="T95">
-        <v>8.582269523235071</v>
+        <v>10.01264777710759</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09092308630168694</v>
+        <v>0.08995581942613708</v>
       </c>
       <c r="W95">
-        <v>0.2143603362500622</v>
+        <v>0.2145884177793169</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3030769543389565</v>
+        <v>0.299852731420457</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2304739716374834</v>
+        <v>0.2323739716374834</v>
       </c>
       <c r="C96">
-        <v>-82.61269641202479</v>
+        <v>-83.96816227991613</v>
       </c>
       <c r="D96">
-        <v>22.09718127686716</v>
+        <v>21.88671410779383</v>
       </c>
       <c r="E96">
-        <v>91.53000780709202</v>
+        <v>92.67500650591002</v>
       </c>
       <c r="F96">
-        <v>107.629877688892</v>
+        <v>108.77487638771</v>
       </c>
       <c r="G96">
         <v>2.92</v>
@@ -9159,37 +9159,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M96">
-        <v>25.37912515904072</v>
+        <v>25.64911585222201</v>
       </c>
       <c r="N96">
-        <v>-17.76912515904072</v>
+        <v>-18.03911585222201</v>
       </c>
       <c r="O96">
-        <v>-5.330737547712217</v>
+        <v>-5.411734755666602</v>
       </c>
       <c r="P96">
-        <v>-12.4383876113285</v>
+        <v>-12.62738109655541</v>
       </c>
       <c r="Q96">
-        <v>0.3616123886714959</v>
+        <v>0.1726189034445955</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4793476487487584</v>
+        <v>0.5660571784985103</v>
       </c>
       <c r="T96">
-        <v>10.01264777710759</v>
+        <v>12.01517733252911</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08995581942613708</v>
+        <v>0.08900891606375669</v>
       </c>
       <c r="W96">
-        <v>0.2145884177793169</v>
+        <v>0.2148116975921662</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.299852731420457</v>
+        <v>0.296696386879189</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2323739716374834</v>
+        <v>0.2342739716374834</v>
       </c>
       <c r="C97">
-        <v>-83.96816227991613</v>
+        <v>-85.31965673599638</v>
       </c>
       <c r="D97">
-        <v>21.88671410779383</v>
+        <v>21.68021835053158</v>
       </c>
       <c r="E97">
-        <v>92.67500650591002</v>
+        <v>93.82000520472802</v>
       </c>
       <c r="F97">
-        <v>108.77487638771</v>
+        <v>109.919875086528</v>
       </c>
       <c r="G97">
         <v>2.92</v>
@@ -9241,37 +9241,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M97">
-        <v>25.64911585222201</v>
+        <v>25.91910654540329</v>
       </c>
       <c r="N97">
-        <v>-18.03911585222201</v>
+        <v>-18.30910654540329</v>
       </c>
       <c r="O97">
-        <v>-5.411734755666602</v>
+        <v>-5.492731963620987</v>
       </c>
       <c r="P97">
-        <v>-12.62738109655541</v>
+        <v>-12.81637458178231</v>
       </c>
       <c r="Q97">
-        <v>0.1726189034445955</v>
+        <v>-0.01637458178230489</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5660571784985103</v>
+        <v>0.6961214731231381</v>
       </c>
       <c r="T97">
-        <v>12.01517733252911</v>
+        <v>15.01897166566139</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08900891606375669</v>
+        <v>0.08808173985475921</v>
       </c>
       <c r="W97">
-        <v>0.2148116975921662</v>
+        <v>0.2150303257422478</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.296696386879189</v>
+        <v>0.2936057995158641</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2342739716374834</v>
+        <v>0.2361739716374834</v>
       </c>
       <c r="C98">
-        <v>-85.31965673599636</v>
+        <v>-86.66729113751435</v>
       </c>
       <c r="D98">
-        <v>21.68021835053158</v>
+        <v>21.47758264783159</v>
       </c>
       <c r="E98">
-        <v>93.82000520472801</v>
+        <v>94.96500390354601</v>
       </c>
       <c r="F98">
-        <v>109.9198750865279</v>
+        <v>111.0648737853459</v>
       </c>
       <c r="G98">
         <v>2.92</v>
@@ -9323,37 +9323,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M98">
-        <v>25.91910654540329</v>
+        <v>26.18909723858457</v>
       </c>
       <c r="N98">
-        <v>-18.30910654540329</v>
+        <v>-18.57909723858457</v>
       </c>
       <c r="O98">
-        <v>-5.492731963620987</v>
+        <v>-5.573729171575372</v>
       </c>
       <c r="P98">
-        <v>-12.8163745817823</v>
+        <v>-13.0053680670092</v>
       </c>
       <c r="Q98">
-        <v>-0.01637458178230133</v>
+        <v>-0.2053680670092</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6961214731231364</v>
+        <v>0.9128952974975152</v>
       </c>
       <c r="T98">
-        <v>15.01897166566135</v>
+        <v>20.02529555421514</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08808173985475924</v>
+        <v>0.08717368068099883</v>
       </c>
       <c r="W98">
-        <v>0.2150303257422478</v>
+        <v>0.2152444460954205</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2936057995158641</v>
+        <v>0.2905789356033295</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2361739716374834</v>
+        <v>0.2380739716374833</v>
       </c>
       <c r="C99">
-        <v>-86.66729113751435</v>
+        <v>-88.01117271703674</v>
       </c>
       <c r="D99">
-        <v>21.47758264783159</v>
+        <v>21.27869976712719</v>
       </c>
       <c r="E99">
-        <v>94.96500390354601</v>
+        <v>96.11000260236401</v>
       </c>
       <c r="F99">
-        <v>111.0648737853459</v>
+        <v>112.2098724841639</v>
       </c>
       <c r="G99">
         <v>2.92</v>
@@ -9405,37 +9405,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M99">
-        <v>26.18909723858457</v>
+        <v>26.45908793176586</v>
       </c>
       <c r="N99">
-        <v>-18.57909723858457</v>
+        <v>-18.84908793176586</v>
       </c>
       <c r="O99">
-        <v>-5.573729171575372</v>
+        <v>-5.654726379529757</v>
       </c>
       <c r="P99">
-        <v>-13.0053680670092</v>
+        <v>-13.1943615522361</v>
       </c>
       <c r="Q99">
-        <v>-0.2053680670092</v>
+        <v>-0.3943615522361004</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9128952974975152</v>
+        <v>1.346442946246273</v>
       </c>
       <c r="T99">
-        <v>20.02529555421514</v>
+        <v>30.03794333132271</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08717368068099883</v>
+        <v>0.08628415332711109</v>
       </c>
       <c r="W99">
-        <v>0.2152444460954205</v>
+        <v>0.2154541966454672</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2905789356033295</v>
+        <v>0.2876138444237036</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2380739716374833</v>
+        <v>0.2399739716374834</v>
       </c>
       <c r="C100">
-        <v>-88.01117271703674</v>
+        <v>-89.35140477166911</v>
       </c>
       <c r="D100">
-        <v>21.27869976712719</v>
+        <v>21.08346641131284</v>
       </c>
       <c r="E100">
-        <v>96.11000260236401</v>
+        <v>97.25500130118201</v>
       </c>
       <c r="F100">
-        <v>112.2098724841639</v>
+        <v>113.3548711829819</v>
       </c>
       <c r="G100">
         <v>2.92</v>
@@ -9487,37 +9487,37 @@
         <v>7.609999999999999</v>
       </c>
       <c r="M100">
-        <v>26.45908793176586</v>
+        <v>26.72907862494714</v>
       </c>
       <c r="N100">
-        <v>-18.84908793176586</v>
+        <v>-19.11907862494714</v>
       </c>
       <c r="O100">
-        <v>-5.654726379529757</v>
+        <v>-5.735723587484142</v>
       </c>
       <c r="P100">
-        <v>-13.1943615522361</v>
+        <v>-13.383355037463</v>
       </c>
       <c r="Q100">
-        <v>-0.3943615522361004</v>
+        <v>-0.5833550374630008</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.346442946246273</v>
+        <v>2.647085892492545</v>
       </c>
       <c r="T100">
-        <v>30.03794333132271</v>
+        <v>60.0758866626454</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08628415332711109</v>
+        <v>0.08541259622279683</v>
       </c>
       <c r="W100">
-        <v>0.2154541966454672</v>
+        <v>0.2156597098106645</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2876138444237036</v>
+        <v>0.2847086540759894</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2399739716374834</v>
-      </c>
-      <c r="C101">
-        <v>-89.35140477166911</v>
-      </c>
-      <c r="D101">
-        <v>21.08346641131284</v>
-      </c>
-      <c r="E101">
-        <v>97.25500130118201</v>
-      </c>
-      <c r="F101">
-        <v>113.3548711829819</v>
-      </c>
-      <c r="G101">
-        <v>2.92</v>
-      </c>
-      <c r="H101">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>20.41</v>
-      </c>
-      <c r="K101">
-        <v>12.8</v>
-      </c>
-      <c r="L101">
-        <v>7.609999999999999</v>
-      </c>
-      <c r="M101">
-        <v>26.72907862494714</v>
-      </c>
-      <c r="N101">
-        <v>-19.11907862494714</v>
-      </c>
-      <c r="O101">
-        <v>-5.735723587484142</v>
-      </c>
-      <c r="P101">
-        <v>-13.383355037463</v>
-      </c>
-      <c r="Q101">
-        <v>-0.5833550374630008</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.647085892492545</v>
-      </c>
-      <c r="T101">
-        <v>60.0758866626454</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08541259622279683</v>
-      </c>
-      <c r="W101">
-        <v>0.2156597098106645</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2847086540759894</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
